--- a/Modbus_Register_Map_DE_V7-3_2026-04(1).xlsx
+++ b/Modbus_Register_Map_DE_V7-3_2026-04(1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://siemens-my.sharepoint.com/personal/malte-benedikt_schroeter_siemens_com/Documents/BA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{6FC972EA-D6E1-49D5-9855-E0690DB85FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79687803-54B3-4C8C-8542-D40BCF939745}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{6FC972EA-D6E1-49D5-9855-E0690DB85FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{977DE913-7BC2-48A4-8D15-890B4C003DD5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{52693526-3C21-4877-AB79-BA724E1391B6}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{52693526-3C21-4877-AB79-BA724E1391B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Messwerte" sheetId="3" r:id="rId1"/>
@@ -5067,6 +5067,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5503,9 +5507,7 @@
       </c>
     </row>
     <row r="2" spans="1:28" ht="336.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28">
-        <v>2560</v>
-      </c>
+      <c r="A2" s="28"/>
       <c r="B2" s="29" t="s">
         <v>679</v>
       </c>
@@ -5583,9 +5585,7 @@
       </c>
     </row>
     <row r="3" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28">
-        <v>2561</v>
-      </c>
+      <c r="A3" s="28"/>
       <c r="B3" s="29" t="s">
         <v>680</v>
       </c>
@@ -5645,9 +5645,7 @@
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
-        <v>2567</v>
-      </c>
+      <c r="A4" s="28"/>
       <c r="B4" s="29" t="s">
         <v>681</v>
       </c>
@@ -5725,9 +5723,7 @@
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" s="28">
-        <v>2572</v>
-      </c>
+      <c r="A5" s="28"/>
       <c r="B5" s="29" t="s">
         <v>682</v>
       </c>
@@ -5789,9 +5785,7 @@
       <c r="AB5" s="30"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
-        <v>2577</v>
-      </c>
+      <c r="A6" s="28"/>
       <c r="B6" s="29" t="s">
         <v>683</v>
       </c>
@@ -5911,9 +5905,7 @@
       <c r="AB7" s="30"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
-        <v>2589</v>
-      </c>
+      <c r="A8" s="28"/>
       <c r="B8" s="29" t="s">
         <v>685</v>
       </c>
@@ -5987,9 +5979,7 @@
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
-        <v>2591</v>
-      </c>
+      <c r="A9" s="28"/>
       <c r="B9" s="29" t="s">
         <v>686</v>
       </c>
@@ -6213,9 +6203,7 @@
       <c r="AB12" s="30"/>
     </row>
     <row r="13" spans="1:28" ht="195" x14ac:dyDescent="0.25">
-      <c r="A13" s="28">
-        <v>2597</v>
-      </c>
+      <c r="A13" s="28"/>
       <c r="B13" s="29" t="s">
         <v>690</v>
       </c>
@@ -6575,9 +6563,7 @@
       <c r="AB19" s="30"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="28">
-        <v>2623</v>
-      </c>
+      <c r="A20" s="28"/>
       <c r="B20" s="29" t="s">
         <v>697</v>
       </c>
@@ -6625,9 +6611,7 @@
       <c r="AB20" s="30"/>
     </row>
     <row r="21" spans="1:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="28">
-        <v>2627</v>
-      </c>
+      <c r="A21" s="28"/>
       <c r="B21" s="29" t="s">
         <v>698</v>
       </c>
@@ -6677,9 +6661,7 @@
       <c r="AB21" s="30"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="28">
-        <v>2628</v>
-      </c>
+      <c r="A22" s="28"/>
       <c r="B22" s="29" t="s">
         <v>699</v>
       </c>
@@ -6934,9 +6916,7 @@
       </c>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A27" s="30">
-        <v>2652</v>
-      </c>
+      <c r="A27" s="30"/>
       <c r="B27" s="29" t="s">
         <v>1351</v>
       </c>
@@ -6984,9 +6964,7 @@
       <c r="AB27" s="30"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A28" s="28">
-        <v>3072</v>
-      </c>
+      <c r="A28" s="28"/>
       <c r="B28" s="29" t="s">
         <v>700</v>
       </c>
@@ -7064,9 +7042,7 @@
       </c>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A29" s="28">
-        <v>3073</v>
-      </c>
+      <c r="A29" s="28"/>
       <c r="B29" s="29" t="s">
         <v>701</v>
       </c>
@@ -7144,9 +7120,7 @@
       </c>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A30" s="28">
-        <v>3074</v>
-      </c>
+      <c r="A30" s="28"/>
       <c r="B30" s="29" t="s">
         <v>702</v>
       </c>
@@ -7206,9 +7180,7 @@
       </c>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A31" s="28">
-        <v>3075</v>
-      </c>
+      <c r="A31" s="28"/>
       <c r="B31" s="29" t="s">
         <v>703</v>
       </c>
@@ -7268,9 +7240,7 @@
       </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A32" s="28">
-        <v>3076</v>
-      </c>
+      <c r="A32" s="28"/>
       <c r="B32" s="29" t="s">
         <v>704</v>
       </c>
@@ -7330,9 +7300,7 @@
       </c>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A33" s="28">
-        <v>3077</v>
-      </c>
+      <c r="A33" s="28"/>
       <c r="B33" s="29" t="s">
         <v>705</v>
       </c>
@@ -7388,9 +7356,7 @@
       <c r="AB33" s="30"/>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A34" s="28">
-        <v>3078</v>
-      </c>
+      <c r="A34" s="28"/>
       <c r="B34" s="29" t="s">
         <v>706</v>
       </c>
@@ -7446,9 +7412,7 @@
       <c r="AB34" s="30"/>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A35" s="28">
-        <v>3079</v>
-      </c>
+      <c r="A35" s="28"/>
       <c r="B35" s="29" t="s">
         <v>707</v>
       </c>
@@ -7504,9 +7468,7 @@
       <c r="AB35" s="30"/>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A36" s="28">
-        <v>3080</v>
-      </c>
+      <c r="A36" s="28"/>
       <c r="B36" s="29" t="s">
         <v>708</v>
       </c>
@@ -7562,9 +7524,7 @@
       <c r="AB36" s="30"/>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A37" s="28">
-        <v>3081</v>
-      </c>
+      <c r="A37" s="28"/>
       <c r="B37" s="29" t="s">
         <v>709</v>
       </c>
@@ -7620,9 +7580,7 @@
       <c r="AB37" s="30"/>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A38" s="28">
-        <v>3082</v>
-      </c>
+      <c r="A38" s="28"/>
       <c r="B38" s="29" t="s">
         <v>710</v>
       </c>
@@ -7900,9 +7858,7 @@
       <c r="AB42" s="30"/>
     </row>
     <row r="43" spans="1:28" ht="105" x14ac:dyDescent="0.25">
-      <c r="A43" s="28">
-        <v>3087</v>
-      </c>
+      <c r="A43" s="28"/>
       <c r="B43" s="29" t="s">
         <v>715</v>
       </c>
@@ -8070,9 +8026,7 @@
       <c r="AB45" s="30"/>
     </row>
     <row r="46" spans="1:28" ht="90" x14ac:dyDescent="0.25">
-      <c r="A46" s="28">
-        <v>3090</v>
-      </c>
+      <c r="A46" s="28"/>
       <c r="B46" s="29" t="s">
         <v>718</v>
       </c>
@@ -8122,9 +8076,7 @@
       <c r="AB46" s="30"/>
     </row>
     <row r="47" spans="1:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="28">
-        <v>3091</v>
-      </c>
+      <c r="A47" s="28"/>
       <c r="B47" s="29" t="s">
         <v>719</v>
       </c>
@@ -8174,9 +8126,7 @@
       <c r="AB47" s="30"/>
     </row>
     <row r="48" spans="1:28" ht="60" x14ac:dyDescent="0.25">
-      <c r="A48" s="28">
-        <v>3092</v>
-      </c>
+      <c r="A48" s="28"/>
       <c r="B48" s="29" t="s">
         <v>1227</v>
       </c>
@@ -8228,9 +8178,7 @@
       <c r="AB48" s="30"/>
     </row>
     <row r="49" spans="1:28" ht="60" x14ac:dyDescent="0.25">
-      <c r="A49" s="28">
-        <v>3093</v>
-      </c>
+      <c r="A49" s="28"/>
       <c r="B49" s="29" t="s">
         <v>1228</v>
       </c>
@@ -8542,9 +8490,7 @@
       </c>
     </row>
     <row r="55" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A55" s="28">
-        <v>3105</v>
-      </c>
+      <c r="A55" s="28"/>
       <c r="B55" s="29" t="s">
         <v>1352</v>
       </c>
@@ -8750,9 +8696,7 @@
       <c r="AB58" s="30"/>
     </row>
     <row r="59" spans="1:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="28">
-        <v>3329</v>
-      </c>
+      <c r="A59" s="28"/>
       <c r="B59" s="29" t="s">
         <v>721</v>
       </c>
@@ -8962,9 +8906,7 @@
       <c r="AB62" s="30"/>
     </row>
     <row r="63" spans="1:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="28">
-        <v>3333</v>
-      </c>
+      <c r="A63" s="28"/>
       <c r="B63" s="29" t="s">
         <v>725</v>
       </c>
@@ -10146,9 +10088,7 @@
       </c>
     </row>
     <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="28">
-        <v>2</v>
-      </c>
+      <c r="A2" s="28"/>
       <c r="B2" s="29" t="s">
         <v>746</v>
       </c>
@@ -10227,9 +10167,7 @@
       </c>
     </row>
     <row r="3" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="28">
-        <v>3</v>
-      </c>
+      <c r="A3" s="28"/>
       <c r="B3" s="29" t="s">
         <v>747</v>
       </c>
@@ -10306,9 +10244,7 @@
       </c>
     </row>
     <row r="4" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
-        <v>4</v>
-      </c>
+      <c r="A4" s="28"/>
       <c r="B4" s="29" t="s">
         <v>748</v>
       </c>
@@ -10385,9 +10321,7 @@
       </c>
     </row>
     <row r="5" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="28">
-        <v>5</v>
-      </c>
+      <c r="A5" s="28"/>
       <c r="B5" s="29" t="s">
         <v>749</v>
       </c>
@@ -10462,9 +10396,7 @@
       </c>
     </row>
     <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
-        <v>6</v>
-      </c>
+      <c r="A6" s="28"/>
       <c r="B6" s="29" t="s">
         <v>750</v>
       </c>
@@ -10541,9 +10473,7 @@
       </c>
     </row>
     <row r="7" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
-        <v>12</v>
-      </c>
+      <c r="A7" s="28"/>
       <c r="B7" s="29" t="s">
         <v>751</v>
       </c>
@@ -10620,9 +10550,7 @@
       </c>
     </row>
     <row r="8" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
-        <v>13</v>
-      </c>
+      <c r="A8" s="28"/>
       <c r="B8" s="29" t="s">
         <v>752</v>
       </c>
@@ -10699,9 +10627,7 @@
       </c>
     </row>
     <row r="9" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
-        <v>14</v>
-      </c>
+      <c r="A9" s="28"/>
       <c r="B9" s="29" t="s">
         <v>753</v>
       </c>
@@ -10778,9 +10704,7 @@
       </c>
     </row>
     <row r="10" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
-        <v>21</v>
-      </c>
+      <c r="A10" s="28"/>
       <c r="B10" s="29" t="s">
         <v>754</v>
       </c>
@@ -10863,9 +10787,7 @@
       </c>
     </row>
     <row r="11" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="28">
-        <v>22</v>
-      </c>
+      <c r="A11" s="28"/>
       <c r="B11" s="29" t="s">
         <v>755</v>
       </c>
@@ -10920,9 +10842,7 @@
       <c r="AC11" s="30"/>
     </row>
     <row r="12" spans="1:29" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="28">
-        <v>23</v>
-      </c>
+      <c r="A12" s="28"/>
       <c r="B12" s="29" t="s">
         <v>756</v>
       </c>
@@ -10981,9 +10901,7 @@
       <c r="AC12" s="30"/>
     </row>
     <row r="13" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="28">
-        <v>24</v>
-      </c>
+      <c r="A13" s="28"/>
       <c r="B13" s="29" t="s">
         <v>757</v>
       </c>
@@ -11064,9 +10982,7 @@
       </c>
     </row>
     <row r="14" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
-        <v>25</v>
-      </c>
+      <c r="A14" s="28"/>
       <c r="B14" s="29" t="s">
         <v>758</v>
       </c>
@@ -11125,9 +11041,7 @@
       </c>
     </row>
     <row r="15" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="28">
-        <v>26</v>
-      </c>
+      <c r="A15" s="28"/>
       <c r="B15" s="29" t="s">
         <v>759</v>
       </c>
@@ -11180,9 +11094,7 @@
       </c>
     </row>
     <row r="16" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
-        <v>27</v>
-      </c>
+      <c r="A16" s="28"/>
       <c r="B16" s="29" t="s">
         <v>760</v>
       </c>
@@ -11263,9 +11175,7 @@
       </c>
     </row>
     <row r="17" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="28">
-        <v>28</v>
-      </c>
+      <c r="A17" s="28"/>
       <c r="B17" s="29" t="s">
         <v>761</v>
       </c>
@@ -11324,9 +11234,7 @@
       </c>
     </row>
     <row r="18" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
-        <v>29</v>
-      </c>
+      <c r="A18" s="28"/>
       <c r="B18" s="29" t="s">
         <v>762</v>
       </c>
@@ -11387,9 +11295,7 @@
       <c r="AC18" s="30"/>
     </row>
     <row r="19" spans="1:29" ht="135" x14ac:dyDescent="0.25">
-      <c r="A19" s="28">
-        <v>30</v>
-      </c>
+      <c r="A19" s="28"/>
       <c r="B19" s="29" t="s">
         <v>763</v>
       </c>
@@ -11470,9 +11376,7 @@
       </c>
     </row>
     <row r="20" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="28">
-        <v>31</v>
-      </c>
+      <c r="A20" s="28"/>
       <c r="B20" s="29" t="s">
         <v>764</v>
       </c>
@@ -11529,9 +11433,7 @@
       <c r="AC20" s="30"/>
     </row>
     <row r="21" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="28">
-        <v>32</v>
-      </c>
+      <c r="A21" s="28"/>
       <c r="B21" s="29" t="s">
         <v>765</v>
       </c>
@@ -11588,9 +11490,7 @@
       <c r="AC21" s="30"/>
     </row>
     <row r="22" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="28">
-        <v>36</v>
-      </c>
+      <c r="A22" s="28"/>
       <c r="B22" s="29" t="s">
         <v>766</v>
       </c>
@@ -11641,9 +11541,7 @@
       <c r="AC22" s="30"/>
     </row>
     <row r="23" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="28">
-        <v>37</v>
-      </c>
+      <c r="A23" s="28"/>
       <c r="B23" s="29" t="s">
         <v>767</v>
       </c>
@@ -11700,9 +11598,7 @@
       <c r="AC23" s="30"/>
     </row>
     <row r="24" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="28">
-        <v>40</v>
-      </c>
+      <c r="A24" s="28"/>
       <c r="B24" s="29" t="s">
         <v>768</v>
       </c>
@@ -11759,9 +11655,7 @@
       <c r="AC24" s="30"/>
     </row>
     <row r="25" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="28">
-        <v>41</v>
-      </c>
+      <c r="A25" s="28"/>
       <c r="B25" s="29" t="s">
         <v>769</v>
       </c>
@@ -11812,9 +11706,7 @@
       <c r="AC25" s="30"/>
     </row>
     <row r="26" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="28">
-        <v>42</v>
-      </c>
+      <c r="A26" s="28"/>
       <c r="B26" s="29" t="s">
         <v>770</v>
       </c>
@@ -11865,9 +11757,7 @@
       <c r="AC26" s="30"/>
     </row>
     <row r="27" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="28">
-        <v>43</v>
-      </c>
+      <c r="A27" s="28"/>
       <c r="B27" s="29" t="s">
         <v>771</v>
       </c>
@@ -11924,9 +11814,7 @@
       <c r="AC27" s="30"/>
     </row>
     <row r="28" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="28">
-        <v>44</v>
-      </c>
+      <c r="A28" s="28"/>
       <c r="B28" s="29" t="s">
         <v>772</v>
       </c>
@@ -11983,9 +11871,7 @@
       <c r="AC28" s="30"/>
     </row>
     <row r="29" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="28">
-        <v>45</v>
-      </c>
+      <c r="A29" s="28"/>
       <c r="B29" s="29" t="s">
         <v>773</v>
       </c>
@@ -12048,9 +11934,7 @@
       <c r="AC29" s="30"/>
     </row>
     <row r="30" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="28">
-        <v>52</v>
-      </c>
+      <c r="A30" s="28"/>
       <c r="B30" s="29" t="s">
         <v>1365</v>
       </c>
@@ -12127,9 +12011,7 @@
       </c>
     </row>
     <row r="31" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="28">
-        <v>53</v>
-      </c>
+      <c r="A31" s="28"/>
       <c r="B31" s="29" t="s">
         <v>1366</v>
       </c>
@@ -12208,9 +12090,7 @@
       </c>
     </row>
     <row r="32" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="28">
-        <v>2562</v>
-      </c>
+      <c r="A32" s="28"/>
       <c r="B32" s="29" t="s">
         <v>774</v>
       </c>
@@ -12277,9 +12157,7 @@
       </c>
     </row>
     <row r="33" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="28">
-        <v>2563</v>
-      </c>
+      <c r="A33" s="28"/>
       <c r="B33" s="29" t="s">
         <v>775</v>
       </c>
@@ -12346,9 +12224,7 @@
       </c>
     </row>
     <row r="34" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="28">
-        <v>2564</v>
-      </c>
+      <c r="A34" s="28"/>
       <c r="B34" s="29" t="s">
         <v>776</v>
       </c>
@@ -12415,9 +12291,7 @@
       </c>
     </row>
     <row r="35" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="28">
-        <v>2568</v>
-      </c>
+      <c r="A35" s="28"/>
       <c r="B35" s="29" t="s">
         <v>777</v>
       </c>
@@ -12500,9 +12374,7 @@
       </c>
     </row>
     <row r="36" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="28">
-        <v>2569</v>
-      </c>
+      <c r="A36" s="28"/>
       <c r="B36" s="29" t="s">
         <v>778</v>
       </c>
@@ -12585,9 +12457,7 @@
       </c>
     </row>
     <row r="37" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="28">
-        <v>2573</v>
-      </c>
+      <c r="A37" s="28"/>
       <c r="B37" s="29" t="s">
         <v>779</v>
       </c>
@@ -12658,9 +12528,7 @@
       <c r="AC37" s="30"/>
     </row>
     <row r="38" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="28">
-        <v>2574</v>
-      </c>
+      <c r="A38" s="28"/>
       <c r="B38" s="29" t="s">
         <v>780</v>
       </c>
@@ -12729,9 +12597,7 @@
       <c r="AC38" s="30"/>
     </row>
     <row r="39" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="28">
-        <v>2578</v>
-      </c>
+      <c r="A39" s="28"/>
       <c r="B39" s="29" t="s">
         <v>781</v>
       </c>
@@ -12802,9 +12668,7 @@
       <c r="AC39" s="30"/>
     </row>
     <row r="40" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="28">
-        <v>2579</v>
-      </c>
+      <c r="A40" s="28"/>
       <c r="B40" s="29" t="s">
         <v>782</v>
       </c>
@@ -12873,9 +12737,7 @@
       <c r="AC40" s="30"/>
     </row>
     <row r="41" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="28">
-        <v>2592</v>
-      </c>
+      <c r="A41" s="28"/>
       <c r="B41" s="29" t="s">
         <v>783</v>
       </c>
@@ -12940,9 +12802,7 @@
       <c r="AC41" s="30"/>
     </row>
     <row r="42" spans="1:29" ht="60" x14ac:dyDescent="0.25">
-      <c r="A42" s="28">
-        <v>2593</v>
-      </c>
+      <c r="A42" s="28"/>
       <c r="B42" s="29" t="s">
         <v>784</v>
       </c>
@@ -13005,9 +12865,7 @@
       <c r="AC42" s="30"/>
     </row>
     <row r="43" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="28">
-        <v>2600</v>
-      </c>
+      <c r="A43" s="28"/>
       <c r="B43" s="29" t="s">
         <v>785</v>
       </c>
@@ -13064,9 +12922,7 @@
       <c r="AC43" s="30"/>
     </row>
     <row r="44" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="28">
-        <v>2601</v>
-      </c>
+      <c r="A44" s="28"/>
       <c r="B44" s="29" t="s">
         <v>786</v>
       </c>
@@ -13121,9 +12977,7 @@
       <c r="AC44" s="30"/>
     </row>
     <row r="45" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="28">
-        <v>2602</v>
-      </c>
+      <c r="A45" s="28"/>
       <c r="B45" s="29" t="s">
         <v>787</v>
       </c>
@@ -13180,9 +13034,7 @@
       <c r="AC45" s="30"/>
     </row>
     <row r="46" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="28">
-        <v>2603</v>
-      </c>
+      <c r="A46" s="28"/>
       <c r="B46" s="29" t="s">
         <v>788</v>
       </c>
@@ -13239,9 +13091,7 @@
       <c r="AC46" s="30"/>
     </row>
     <row r="47" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="28">
-        <v>2609</v>
-      </c>
+      <c r="A47" s="28"/>
       <c r="B47" s="29" t="s">
         <v>789</v>
       </c>
@@ -13316,9 +13166,7 @@
       </c>
     </row>
     <row r="48" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="28">
-        <v>2624</v>
-      </c>
+      <c r="A48" s="28"/>
       <c r="B48" s="29" t="s">
         <v>790</v>
       </c>
@@ -13375,9 +13223,7 @@
       <c r="AC48" s="30"/>
     </row>
     <row r="49" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="28">
-        <v>2625</v>
-      </c>
+      <c r="A49" s="28"/>
       <c r="B49" s="29" t="s">
         <v>791</v>
       </c>
@@ -13434,9 +13280,7 @@
       <c r="AC49" s="30"/>
     </row>
     <row r="50" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="28">
-        <v>2626</v>
-      </c>
+      <c r="A50" s="28"/>
       <c r="B50" s="29" t="s">
         <v>792</v>
       </c>
@@ -13493,9 +13337,7 @@
       <c r="AC50" s="30"/>
     </row>
     <row r="51" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="30">
-        <v>2632</v>
-      </c>
+      <c r="A51" s="30"/>
       <c r="B51" s="29" t="s">
         <v>1243</v>
       </c>
@@ -13550,9 +13392,7 @@
       <c r="AC51" s="30"/>
     </row>
     <row r="52" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="30">
-        <v>2633</v>
-      </c>
+      <c r="A52" s="30"/>
       <c r="B52" s="29" t="s">
         <v>1244</v>
       </c>
@@ -13605,9 +13445,7 @@
       <c r="AC52" s="30"/>
     </row>
     <row r="53" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="30">
-        <v>2634</v>
-      </c>
+      <c r="A53" s="30"/>
       <c r="B53" s="29" t="s">
         <v>1245</v>
       </c>
@@ -13662,9 +13500,7 @@
       <c r="AC53" s="30"/>
     </row>
     <row r="54" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="30">
-        <v>2635</v>
-      </c>
+      <c r="A54" s="30"/>
       <c r="B54" s="29" t="s">
         <v>1246</v>
       </c>
@@ -13717,9 +13553,7 @@
       <c r="AC54" s="30"/>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A55" s="28">
-        <v>3584</v>
-      </c>
+      <c r="A55" s="28"/>
       <c r="B55" s="29" t="s">
         <v>793</v>
       </c>
@@ -13774,9 +13608,7 @@
       <c r="AC55" s="30"/>
     </row>
     <row r="56" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="28">
-        <v>3585</v>
-      </c>
+      <c r="A56" s="28"/>
       <c r="B56" s="29" t="s">
         <v>794</v>
       </c>
@@ -13859,9 +13691,7 @@
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A57" s="28">
-        <v>3586</v>
-      </c>
+      <c r="A57" s="28"/>
       <c r="B57" s="29" t="s">
         <v>795</v>
       </c>
@@ -13944,9 +13774,7 @@
       </c>
     </row>
     <row r="58" spans="1:29" ht="120" x14ac:dyDescent="0.25">
-      <c r="A58" s="28">
-        <v>3587</v>
-      </c>
+      <c r="A58" s="28"/>
       <c r="B58" s="29" t="s">
         <v>796</v>
       </c>
@@ -14029,9 +13857,7 @@
       </c>
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A59" s="28">
-        <v>3588</v>
-      </c>
+      <c r="A59" s="28"/>
       <c r="B59" s="29" t="s">
         <v>797</v>
       </c>
@@ -14114,9 +13940,7 @@
       </c>
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A60" s="28">
-        <v>3589</v>
-      </c>
+      <c r="A60" s="28"/>
       <c r="B60" s="29" t="s">
         <v>798</v>
       </c>
@@ -14191,9 +14015,7 @@
       </c>
     </row>
     <row r="61" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="28">
-        <v>3591</v>
-      </c>
+      <c r="A61" s="28"/>
       <c r="B61" s="29" t="s">
         <v>799</v>
       </c>
@@ -14260,9 +14082,7 @@
       </c>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A62" s="28">
-        <v>3592</v>
-      </c>
+      <c r="A62" s="28"/>
       <c r="B62" s="29" t="s">
         <v>800</v>
       </c>
@@ -14329,9 +14149,7 @@
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A63" s="28">
-        <v>3593</v>
-      </c>
+      <c r="A63" s="28"/>
       <c r="B63" s="29" t="s">
         <v>801</v>
       </c>
@@ -14400,9 +14218,7 @@
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A64" s="28">
-        <v>3594</v>
-      </c>
+      <c r="A64" s="28"/>
       <c r="B64" s="29" t="s">
         <v>802</v>
       </c>
@@ -14469,9 +14285,7 @@
       </c>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A65" s="28">
-        <v>3597</v>
-      </c>
+      <c r="A65" s="28"/>
       <c r="B65" s="29" t="s">
         <v>803</v>
       </c>
@@ -14538,9 +14352,7 @@
       </c>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A66" s="28">
-        <v>3598</v>
-      </c>
+      <c r="A66" s="28"/>
       <c r="B66" s="29" t="s">
         <v>804</v>
       </c>
@@ -14607,9 +14419,7 @@
       </c>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A67" s="28">
-        <v>3599</v>
-      </c>
+      <c r="A67" s="28"/>
       <c r="B67" s="29" t="s">
         <v>805</v>
       </c>
@@ -14676,9 +14486,7 @@
       </c>
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A68" s="28">
-        <v>3602</v>
-      </c>
+      <c r="A68" s="28"/>
       <c r="B68" s="29" t="s">
         <v>806</v>
       </c>
@@ -14745,9 +14553,7 @@
       </c>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A69" s="28">
-        <v>3603</v>
-      </c>
+      <c r="A69" s="28"/>
       <c r="B69" s="29" t="s">
         <v>807</v>
       </c>
@@ -14814,9 +14620,7 @@
       </c>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A70" s="28">
-        <v>3604</v>
-      </c>
+      <c r="A70" s="28"/>
       <c r="B70" s="29" t="s">
         <v>808</v>
       </c>
@@ -14883,9 +14687,7 @@
       </c>
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A71" s="28">
-        <v>3607</v>
-      </c>
+      <c r="A71" s="28"/>
       <c r="B71" s="29" t="s">
         <v>809</v>
       </c>
@@ -14952,9 +14754,7 @@
       </c>
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A72" s="28">
-        <v>3608</v>
-      </c>
+      <c r="A72" s="28"/>
       <c r="B72" s="29" t="s">
         <v>810</v>
       </c>
@@ -15023,9 +14823,7 @@
       </c>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A73" s="28">
-        <v>3609</v>
-      </c>
+      <c r="A73" s="28"/>
       <c r="B73" s="29" t="s">
         <v>811</v>
       </c>
@@ -15092,9 +14890,7 @@
       </c>
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A74" s="28">
-        <v>3612</v>
-      </c>
+      <c r="A74" s="28"/>
       <c r="B74" s="29" t="s">
         <v>812</v>
       </c>
@@ -15155,9 +14951,7 @@
       <c r="AC74" s="30"/>
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A75" s="28">
-        <v>3613</v>
-      </c>
+      <c r="A75" s="28"/>
       <c r="B75" s="29" t="s">
         <v>813</v>
       </c>
@@ -15218,9 +15012,7 @@
       <c r="AC75" s="30"/>
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A76" s="28">
-        <v>3614</v>
-      </c>
+      <c r="A76" s="28"/>
       <c r="B76" s="29" t="s">
         <v>814</v>
       </c>
@@ -15281,9 +15073,7 @@
       <c r="AC76" s="30"/>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A77" s="28">
-        <v>3617</v>
-      </c>
+      <c r="A77" s="28"/>
       <c r="B77" s="29" t="s">
         <v>815</v>
       </c>
@@ -15344,9 +15134,7 @@
       <c r="AC77" s="30"/>
     </row>
     <row r="78" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A78" s="28">
-        <v>3618</v>
-      </c>
+      <c r="A78" s="28"/>
       <c r="B78" s="29" t="s">
         <v>816</v>
       </c>
@@ -15407,9 +15195,7 @@
       <c r="AC78" s="30"/>
     </row>
     <row r="79" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A79" s="28">
-        <v>3619</v>
-      </c>
+      <c r="A79" s="28"/>
       <c r="B79" s="29" t="s">
         <v>817</v>
       </c>
@@ -15470,9 +15256,7 @@
       <c r="AC79" s="30"/>
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A80" s="28">
-        <v>3622</v>
-      </c>
+      <c r="A80" s="28"/>
       <c r="B80" s="29" t="s">
         <v>818</v>
       </c>
@@ -15533,9 +15317,7 @@
       <c r="AC80" s="30"/>
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A81" s="28">
-        <v>3623</v>
-      </c>
+      <c r="A81" s="28"/>
       <c r="B81" s="29" t="s">
         <v>819</v>
       </c>
@@ -15596,9 +15378,7 @@
       <c r="AC81" s="30"/>
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A82" s="28">
-        <v>3624</v>
-      </c>
+      <c r="A82" s="28"/>
       <c r="B82" s="29" t="s">
         <v>820</v>
       </c>
@@ -15659,9 +15439,7 @@
       <c r="AC82" s="30"/>
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A83" s="28">
-        <v>3627</v>
-      </c>
+      <c r="A83" s="28"/>
       <c r="B83" s="29" t="s">
         <v>821</v>
       </c>
@@ -15722,9 +15500,7 @@
       <c r="AC83" s="30"/>
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A84" s="28">
-        <v>3628</v>
-      </c>
+      <c r="A84" s="28"/>
       <c r="B84" s="29" t="s">
         <v>822</v>
       </c>
@@ -15785,9 +15561,7 @@
       <c r="AC84" s="30"/>
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A85" s="28">
-        <v>3629</v>
-      </c>
+      <c r="A85" s="28"/>
       <c r="B85" s="29" t="s">
         <v>823</v>
       </c>
@@ -15848,9 +15622,7 @@
       <c r="AC85" s="30"/>
     </row>
     <row r="86" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A86" s="28">
-        <v>3632</v>
-      </c>
+      <c r="A86" s="28"/>
       <c r="B86" s="29" t="s">
         <v>824</v>
       </c>
@@ -15911,9 +15683,7 @@
       <c r="AC86" s="30"/>
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A87" s="28">
-        <v>3633</v>
-      </c>
+      <c r="A87" s="28"/>
       <c r="B87" s="29" t="s">
         <v>825</v>
       </c>
@@ -15978,9 +15748,7 @@
       <c r="AC87" s="30"/>
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A88" s="28">
-        <v>3634</v>
-      </c>
+      <c r="A88" s="28"/>
       <c r="B88" s="29" t="s">
         <v>826</v>
       </c>
@@ -16055,9 +15823,7 @@
       </c>
     </row>
     <row r="89" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A89" s="28">
-        <v>3635</v>
-      </c>
+      <c r="A89" s="28"/>
       <c r="B89" s="29" t="s">
         <v>827</v>
       </c>
@@ -16118,9 +15884,7 @@
       <c r="AC89" s="30"/>
     </row>
     <row r="90" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A90" s="28">
-        <v>3636</v>
-      </c>
+      <c r="A90" s="28"/>
       <c r="B90" s="29" t="s">
         <v>828</v>
       </c>
@@ -16183,9 +15947,7 @@
       <c r="AC90" s="30"/>
     </row>
     <row r="91" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A91" s="28">
-        <v>3637</v>
-      </c>
+      <c r="A91" s="28"/>
       <c r="B91" s="29" t="s">
         <v>829</v>
       </c>
@@ -16242,9 +16004,7 @@
       <c r="AC91" s="30"/>
     </row>
     <row r="92" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A92" s="28">
-        <v>3638</v>
-      </c>
+      <c r="A92" s="28"/>
       <c r="B92" s="29" t="s">
         <v>830</v>
       </c>
@@ -16303,9 +16063,7 @@
       <c r="AC92" s="30"/>
     </row>
     <row r="93" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A93" s="28">
-        <v>3639</v>
-      </c>
+      <c r="A93" s="28"/>
       <c r="B93" s="29" t="s">
         <v>831</v>
       </c>
@@ -16364,9 +16122,7 @@
       <c r="AC93" s="30"/>
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A94" s="28">
-        <v>3640</v>
-      </c>
+      <c r="A94" s="28"/>
       <c r="B94" s="29" t="s">
         <v>832</v>
       </c>
@@ -16425,9 +16181,7 @@
       <c r="AC94" s="30"/>
     </row>
     <row r="95" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A95" s="28">
-        <v>3641</v>
-      </c>
+      <c r="A95" s="28"/>
       <c r="B95" s="29" t="s">
         <v>833</v>
       </c>
@@ -16488,9 +16242,7 @@
       <c r="AC95" s="30"/>
     </row>
     <row r="96" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A96" s="28">
-        <v>3642</v>
-      </c>
+      <c r="A96" s="28"/>
       <c r="B96" s="29" t="s">
         <v>834</v>
       </c>
@@ -16549,9 +16301,7 @@
       <c r="AC96" s="30"/>
     </row>
     <row r="97" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A97" s="28">
-        <v>3643</v>
-      </c>
+      <c r="A97" s="28"/>
       <c r="B97" s="29" t="s">
         <v>835</v>
       </c>
@@ -16608,9 +16358,7 @@
       <c r="AC97" s="30"/>
     </row>
     <row r="98" spans="1:29" ht="165" x14ac:dyDescent="0.25">
-      <c r="A98" s="28">
-        <v>3644</v>
-      </c>
+      <c r="A98" s="28"/>
       <c r="B98" s="29" t="s">
         <v>836</v>
       </c>
@@ -16667,9 +16415,7 @@
       <c r="AC98" s="30"/>
     </row>
     <row r="99" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A99" s="28">
-        <v>3646</v>
-      </c>
+      <c r="A99" s="28"/>
       <c r="B99" s="29" t="s">
         <v>837</v>
       </c>
@@ -16726,9 +16472,7 @@
       <c r="AC99" s="30"/>
     </row>
     <row r="100" spans="1:29" ht="135" x14ac:dyDescent="0.25">
-      <c r="A100" s="28">
-        <v>3647</v>
-      </c>
+      <c r="A100" s="28"/>
       <c r="B100" s="29" t="s">
         <v>838</v>
       </c>
@@ -16785,9 +16529,7 @@
       <c r="AC100" s="30"/>
     </row>
     <row r="101" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A101" s="28">
-        <v>3648</v>
-      </c>
+      <c r="A101" s="28"/>
       <c r="B101" s="29" t="s">
         <v>839</v>
       </c>
@@ -16844,9 +16586,7 @@
       <c r="AC101" s="30"/>
     </row>
     <row r="102" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A102" s="28">
-        <v>3649</v>
-      </c>
+      <c r="A102" s="28"/>
       <c r="B102" s="29" t="s">
         <v>840</v>
       </c>
@@ -16905,9 +16645,7 @@
       <c r="AC102" s="30"/>
     </row>
     <row r="103" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A103" s="28">
-        <v>3650</v>
-      </c>
+      <c r="A103" s="28"/>
       <c r="B103" s="29" t="s">
         <v>841</v>
       </c>
@@ -16966,9 +16704,7 @@
       <c r="AC103" s="30"/>
     </row>
     <row r="104" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A104" s="28">
-        <v>3651</v>
-      </c>
+      <c r="A104" s="28"/>
       <c r="B104" s="29" t="s">
         <v>842</v>
       </c>
@@ -17029,9 +16765,7 @@
       <c r="AC104" s="30"/>
     </row>
     <row r="105" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A105" s="28">
-        <v>3652</v>
-      </c>
+      <c r="A105" s="28"/>
       <c r="B105" s="29" t="s">
         <v>843</v>
       </c>
@@ -17088,9 +16822,7 @@
       <c r="AC105" s="30"/>
     </row>
     <row r="106" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A106" s="28">
-        <v>3653</v>
-      </c>
+      <c r="A106" s="28"/>
       <c r="B106" s="29" t="s">
         <v>844</v>
       </c>
@@ -17147,9 +16879,7 @@
       <c r="AC106" s="30"/>
     </row>
     <row r="107" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A107" s="28">
-        <v>3654</v>
-      </c>
+      <c r="A107" s="28"/>
       <c r="B107" s="29" t="s">
         <v>845</v>
       </c>
@@ -17206,9 +16936,7 @@
       <c r="AC107" s="30"/>
     </row>
     <row r="108" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A108" s="28">
-        <v>3655</v>
-      </c>
+      <c r="A108" s="28"/>
       <c r="B108" s="29" t="s">
         <v>846</v>
       </c>
@@ -17265,9 +16993,7 @@
       <c r="AC108" s="30"/>
     </row>
     <row r="109" spans="1:29" ht="75" x14ac:dyDescent="0.25">
-      <c r="A109" s="28">
-        <v>3657</v>
-      </c>
+      <c r="A109" s="28"/>
       <c r="B109" s="29" t="s">
         <v>1248</v>
       </c>
@@ -17318,9 +17044,7 @@
       <c r="AC109" s="30"/>
     </row>
     <row r="110" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A110" s="28">
-        <v>3658</v>
-      </c>
+      <c r="A110" s="28"/>
       <c r="B110" s="29" t="s">
         <v>847</v>
       </c>
@@ -17377,9 +17101,7 @@
       <c r="AC110" s="30"/>
     </row>
     <row r="111" spans="1:29" ht="120" x14ac:dyDescent="0.25">
-      <c r="A111" s="28">
-        <v>3659</v>
-      </c>
+      <c r="A111" s="28"/>
       <c r="B111" s="29" t="s">
         <v>848</v>
       </c>
@@ -17432,9 +17154,7 @@
       <c r="AC111" s="30"/>
     </row>
     <row r="112" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A112" s="28">
-        <v>3660</v>
-      </c>
+      <c r="A112" s="28"/>
       <c r="B112" s="29" t="s">
         <v>1356</v>
       </c>
@@ -17491,9 +17211,7 @@
       <c r="AC112" s="30"/>
     </row>
     <row r="113" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A113" s="28">
-        <v>3663</v>
-      </c>
+      <c r="A113" s="28"/>
       <c r="B113" s="29" t="s">
         <v>1251</v>
       </c>
@@ -17548,9 +17266,7 @@
       <c r="AC113" s="30"/>
     </row>
     <row r="114" spans="1:29" ht="165" x14ac:dyDescent="0.25">
-      <c r="A114" s="28">
-        <v>3664</v>
-      </c>
+      <c r="A114" s="28"/>
       <c r="B114" s="29" t="s">
         <v>1252</v>
       </c>
@@ -17605,9 +17321,7 @@
       <c r="AC114" s="30"/>
     </row>
     <row r="115" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="20">
-        <v>3667</v>
-      </c>
+      <c r="A115" s="20"/>
       <c r="B115" s="21" t="s">
         <v>1385</v>
       </c>
@@ -17662,9 +17376,7 @@
       <c r="AC115" s="19"/>
     </row>
     <row r="116" spans="1:29" ht="120" x14ac:dyDescent="0.25">
-      <c r="A116" s="28">
-        <v>5120</v>
-      </c>
+      <c r="A116" s="28"/>
       <c r="B116" s="29" t="s">
         <v>849</v>
       </c>
@@ -17721,9 +17433,7 @@
       <c r="AC116" s="30"/>
     </row>
     <row r="117" spans="1:29" ht="165" x14ac:dyDescent="0.25">
-      <c r="A117" s="28">
-        <v>5121</v>
-      </c>
+      <c r="A117" s="28"/>
       <c r="B117" s="29" t="s">
         <v>850</v>
       </c>
@@ -17782,9 +17492,7 @@
       <c r="AC117" s="30"/>
     </row>
     <row r="118" spans="1:29" ht="90" x14ac:dyDescent="0.25">
-      <c r="A118" s="28">
-        <v>5122</v>
-      </c>
+      <c r="A118" s="28"/>
       <c r="B118" s="29" t="s">
         <v>851</v>
       </c>
@@ -17841,9 +17549,7 @@
       <c r="AC118" s="30"/>
     </row>
     <row r="119" spans="1:29" ht="180" x14ac:dyDescent="0.25">
-      <c r="A119" s="28">
-        <v>5123</v>
-      </c>
+      <c r="A119" s="28"/>
       <c r="B119" s="29" t="s">
         <v>852</v>
       </c>
@@ -17900,9 +17606,7 @@
       <c r="AC119" s="30"/>
     </row>
     <row r="120" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A120" s="28">
-        <v>5124</v>
-      </c>
+      <c r="A120" s="28"/>
       <c r="B120" s="29" t="s">
         <v>853</v>
       </c>
@@ -17963,9 +17667,7 @@
       <c r="AC120" s="30"/>
     </row>
     <row r="121" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A121" s="28">
-        <v>5125</v>
-      </c>
+      <c r="A121" s="28"/>
       <c r="B121" s="29" t="s">
         <v>854</v>
       </c>
@@ -18024,9 +17726,7 @@
       <c r="AC121" s="30"/>
     </row>
     <row r="122" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A122" s="28">
-        <v>5126</v>
-      </c>
+      <c r="A122" s="28"/>
       <c r="B122" s="29" t="s">
         <v>855</v>
       </c>
@@ -18087,9 +17787,7 @@
       <c r="AC122" s="30"/>
     </row>
     <row r="123" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A123" s="28">
-        <v>5127</v>
-      </c>
+      <c r="A123" s="28"/>
       <c r="B123" s="29" t="s">
         <v>856</v>
       </c>
@@ -18150,9 +17848,7 @@
       <c r="AC123" s="30"/>
     </row>
     <row r="124" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A124" s="28">
-        <v>5128</v>
-      </c>
+      <c r="A124" s="28"/>
       <c r="B124" s="29" t="s">
         <v>857</v>
       </c>
@@ -18213,9 +17909,7 @@
       <c r="AC124" s="30"/>
     </row>
     <row r="125" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A125" s="28">
-        <v>5129</v>
-      </c>
+      <c r="A125" s="28"/>
       <c r="B125" s="29" t="s">
         <v>858</v>
       </c>
@@ -18276,9 +17970,7 @@
       <c r="AC125" s="30"/>
     </row>
     <row r="126" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A126" s="28">
-        <v>5130</v>
-      </c>
+      <c r="A126" s="28"/>
       <c r="B126" s="29" t="s">
         <v>859</v>
       </c>
@@ -18337,9 +18029,7 @@
       <c r="AC126" s="30"/>
     </row>
     <row r="127" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A127" s="28">
-        <v>5131</v>
-      </c>
+      <c r="A127" s="28"/>
       <c r="B127" s="29" t="s">
         <v>860</v>
       </c>
@@ -18398,9 +18088,7 @@
       <c r="AC127" s="30"/>
     </row>
     <row r="128" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="28">
-        <v>5132</v>
-      </c>
+      <c r="A128" s="28"/>
       <c r="B128" s="29" t="s">
         <v>861</v>
       </c>
@@ -18463,9 +18151,7 @@
       <c r="AC128" s="30"/>
     </row>
     <row r="129" spans="1:29" ht="135" x14ac:dyDescent="0.25">
-      <c r="A129" s="28">
-        <v>5133</v>
-      </c>
+      <c r="A129" s="28"/>
       <c r="B129" s="29" t="s">
         <v>862</v>
       </c>
@@ -18526,9 +18212,7 @@
       <c r="AC129" s="30"/>
     </row>
     <row r="130" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A130" s="28">
-        <v>5134</v>
-      </c>
+      <c r="A130" s="28"/>
       <c r="B130" s="29" t="s">
         <v>863</v>
       </c>
@@ -18585,9 +18269,7 @@
       <c r="AC130" s="30"/>
     </row>
     <row r="131" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A131" s="28">
-        <v>5135</v>
-      </c>
+      <c r="A131" s="28"/>
       <c r="B131" s="29" t="s">
         <v>864</v>
       </c>
@@ -18644,9 +18326,7 @@
       <c r="AC131" s="30"/>
     </row>
     <row r="132" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A132" s="28">
-        <v>5136</v>
-      </c>
+      <c r="A132" s="28"/>
       <c r="B132" s="29" t="s">
         <v>865</v>
       </c>
@@ -18707,9 +18387,7 @@
       <c r="AC132" s="30"/>
     </row>
     <row r="133" spans="1:29" ht="90" x14ac:dyDescent="0.25">
-      <c r="A133" s="28">
-        <v>5137</v>
-      </c>
+      <c r="A133" s="28"/>
       <c r="B133" s="29" t="s">
         <v>866</v>
       </c>
@@ -18768,9 +18446,7 @@
       <c r="AC133" s="30"/>
     </row>
     <row r="134" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A134" s="28">
-        <v>5138</v>
-      </c>
+      <c r="A134" s="28"/>
       <c r="B134" s="29" t="s">
         <v>867</v>
       </c>
@@ -18825,9 +18501,7 @@
       <c r="AC134" s="30"/>
     </row>
     <row r="135" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A135" s="28">
-        <v>5139</v>
-      </c>
+      <c r="A135" s="28"/>
       <c r="B135" s="29" t="s">
         <v>868</v>
       </c>
@@ -18882,9 +18556,7 @@
       <c r="AC135" s="30"/>
     </row>
     <row r="136" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A136" s="28">
-        <v>5140</v>
-      </c>
+      <c r="A136" s="28"/>
       <c r="B136" s="29" t="s">
         <v>869</v>
       </c>
@@ -18943,9 +18615,7 @@
       <c r="AC136" s="30"/>
     </row>
     <row r="137" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A137" s="28">
-        <v>5141</v>
-      </c>
+      <c r="A137" s="28"/>
       <c r="B137" s="29" t="s">
         <v>870</v>
       </c>
@@ -19002,9 +18672,7 @@
       <c r="AC137" s="30"/>
     </row>
     <row r="138" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A138" s="28">
-        <v>5142</v>
-      </c>
+      <c r="A138" s="28"/>
       <c r="B138" s="29" t="s">
         <v>871</v>
       </c>
@@ -19061,9 +18729,7 @@
       <c r="AC138" s="30"/>
     </row>
     <row r="139" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A139" s="28">
-        <v>5143</v>
-      </c>
+      <c r="A139" s="28"/>
       <c r="B139" s="29" t="s">
         <v>872</v>
       </c>
@@ -19120,9 +18786,7 @@
       <c r="AC139" s="30"/>
     </row>
     <row r="140" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A140" s="28">
-        <v>5144</v>
-      </c>
+      <c r="A140" s="28"/>
       <c r="B140" s="29" t="s">
         <v>873</v>
       </c>
@@ -19179,9 +18843,7 @@
       <c r="AC140" s="30"/>
     </row>
     <row r="141" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A141" s="28">
-        <v>5145</v>
-      </c>
+      <c r="A141" s="28"/>
       <c r="B141" s="29" t="s">
         <v>874</v>
       </c>
@@ -19240,9 +18902,7 @@
       <c r="AC141" s="30"/>
     </row>
     <row r="142" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A142" s="28">
-        <v>5146</v>
-      </c>
+      <c r="A142" s="28"/>
       <c r="B142" s="29" t="s">
         <v>875</v>
       </c>
@@ -19299,9 +18959,7 @@
       <c r="AC142" s="30"/>
     </row>
     <row r="143" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A143" s="28">
-        <v>5147</v>
-      </c>
+      <c r="A143" s="28"/>
       <c r="B143" s="29" t="s">
         <v>876</v>
       </c>
@@ -19360,9 +19018,7 @@
       <c r="AC143" s="30"/>
     </row>
     <row r="144" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A144" s="28">
-        <v>5148</v>
-      </c>
+      <c r="A144" s="28"/>
       <c r="B144" s="29" t="s">
         <v>877</v>
       </c>
@@ -19419,9 +19075,7 @@
       <c r="AC144" s="30"/>
     </row>
     <row r="145" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A145" s="28">
-        <v>5149</v>
-      </c>
+      <c r="A145" s="28"/>
       <c r="B145" s="29" t="s">
         <v>878</v>
       </c>
@@ -19480,9 +19134,7 @@
       <c r="AC145" s="30"/>
     </row>
     <row r="146" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A146" s="28">
-        <v>5150</v>
-      </c>
+      <c r="A146" s="28"/>
       <c r="B146" s="29" t="s">
         <v>879</v>
       </c>
@@ -19539,9 +19191,7 @@
       <c r="AC146" s="30"/>
     </row>
     <row r="147" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A147" s="28">
-        <v>5151</v>
-      </c>
+      <c r="A147" s="28"/>
       <c r="B147" s="29" t="s">
         <v>880</v>
       </c>
@@ -19598,9 +19248,7 @@
       <c r="AC147" s="30"/>
     </row>
     <row r="148" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A148" s="28">
-        <v>5152</v>
-      </c>
+      <c r="A148" s="28"/>
       <c r="B148" s="29" t="s">
         <v>881</v>
       </c>
@@ -19657,9 +19305,7 @@
       <c r="AC148" s="30"/>
     </row>
     <row r="149" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A149" s="28">
-        <v>5153</v>
-      </c>
+      <c r="A149" s="28"/>
       <c r="B149" s="29" t="s">
         <v>882</v>
       </c>
@@ -19716,9 +19362,7 @@
       <c r="AC149" s="30"/>
     </row>
     <row r="150" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A150" s="28">
-        <v>5154</v>
-      </c>
+      <c r="A150" s="28"/>
       <c r="B150" s="29" t="s">
         <v>883</v>
       </c>
@@ -19777,9 +19421,7 @@
       <c r="AC150" s="30"/>
     </row>
     <row r="151" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A151" s="28">
-        <v>5155</v>
-      </c>
+      <c r="A151" s="28"/>
       <c r="B151" s="29" t="s">
         <v>884</v>
       </c>
@@ -19836,9 +19478,7 @@
       <c r="AC151" s="30"/>
     </row>
     <row r="152" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A152" s="28">
-        <v>5156</v>
-      </c>
+      <c r="A152" s="28"/>
       <c r="B152" s="29" t="s">
         <v>885</v>
       </c>
@@ -19897,9 +19537,7 @@
       <c r="AC152" s="30"/>
     </row>
     <row r="153" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A153" s="28">
-        <v>5157</v>
-      </c>
+      <c r="A153" s="28"/>
       <c r="B153" s="29" t="s">
         <v>886</v>
       </c>
@@ -19956,9 +19594,7 @@
       <c r="AC153" s="30"/>
     </row>
     <row r="154" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A154" s="28">
-        <v>5158</v>
-      </c>
+      <c r="A154" s="28"/>
       <c r="B154" s="29" t="s">
         <v>887</v>
       </c>
@@ -20017,9 +19653,7 @@
       <c r="AC154" s="30"/>
     </row>
     <row r="155" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A155" s="28">
-        <v>5159</v>
-      </c>
+      <c r="A155" s="28"/>
       <c r="B155" s="29" t="s">
         <v>888</v>
       </c>
@@ -20076,9 +19710,7 @@
       <c r="AC155" s="30"/>
     </row>
     <row r="156" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A156" s="28">
-        <v>5160</v>
-      </c>
+      <c r="A156" s="28"/>
       <c r="B156" s="29" t="s">
         <v>889</v>
       </c>
@@ -20135,9 +19767,7 @@
       <c r="AC156" s="30"/>
     </row>
     <row r="157" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A157" s="28">
-        <v>5161</v>
-      </c>
+      <c r="A157" s="28"/>
       <c r="B157" s="29" t="s">
         <v>890</v>
       </c>
@@ -20194,9 +19824,7 @@
       <c r="AC157" s="30"/>
     </row>
     <row r="158" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A158" s="28">
-        <v>5162</v>
-      </c>
+      <c r="A158" s="28"/>
       <c r="B158" s="29" t="s">
         <v>891</v>
       </c>
@@ -20253,9 +19881,7 @@
       <c r="AC158" s="30"/>
     </row>
     <row r="159" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A159" s="28">
-        <v>5163</v>
-      </c>
+      <c r="A159" s="28"/>
       <c r="B159" s="29" t="s">
         <v>892</v>
       </c>
@@ -20314,9 +19940,7 @@
       <c r="AC159" s="30"/>
     </row>
     <row r="160" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A160" s="28">
-        <v>5164</v>
-      </c>
+      <c r="A160" s="28"/>
       <c r="B160" s="29" t="s">
         <v>893</v>
       </c>
@@ -20373,9 +19997,7 @@
       <c r="AC160" s="30"/>
     </row>
     <row r="161" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A161" s="28">
-        <v>5165</v>
-      </c>
+      <c r="A161" s="28"/>
       <c r="B161" s="29" t="s">
         <v>894</v>
       </c>
@@ -20434,9 +20056,7 @@
       <c r="AC161" s="30"/>
     </row>
     <row r="162" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A162" s="28">
-        <v>5166</v>
-      </c>
+      <c r="A162" s="28"/>
       <c r="B162" s="29" t="s">
         <v>895</v>
       </c>
@@ -20493,9 +20113,7 @@
       <c r="AC162" s="30"/>
     </row>
     <row r="163" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A163" s="28">
-        <v>5167</v>
-      </c>
+      <c r="A163" s="28"/>
       <c r="B163" s="29" t="s">
         <v>896</v>
       </c>
@@ -20554,9 +20172,7 @@
       <c r="AC163" s="30"/>
     </row>
     <row r="164" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A164" s="28">
-        <v>5168</v>
-      </c>
+      <c r="A164" s="28"/>
       <c r="B164" s="29" t="s">
         <v>897</v>
       </c>
@@ -20613,9 +20229,7 @@
       <c r="AC164" s="30"/>
     </row>
     <row r="165" spans="1:29" ht="90" x14ac:dyDescent="0.25">
-      <c r="A165" s="28">
-        <v>5170</v>
-      </c>
+      <c r="A165" s="28"/>
       <c r="B165" s="29" t="s">
         <v>898</v>
       </c>
@@ -20672,9 +20286,7 @@
       <c r="AC165" s="30"/>
     </row>
     <row r="166" spans="1:29" ht="135" x14ac:dyDescent="0.25">
-      <c r="A166" s="28">
-        <v>5171</v>
-      </c>
+      <c r="A166" s="28"/>
       <c r="B166" s="29" t="s">
         <v>899</v>
       </c>
@@ -20731,9 +20343,7 @@
       <c r="AC166" s="30"/>
     </row>
     <row r="167" spans="1:29" ht="225" x14ac:dyDescent="0.25">
-      <c r="A167" s="28">
-        <v>5173</v>
-      </c>
+      <c r="A167" s="28"/>
       <c r="B167" s="29" t="s">
         <v>900</v>
       </c>
@@ -20790,9 +20400,7 @@
       <c r="AC167" s="30"/>
     </row>
     <row r="168" spans="1:29" ht="135" x14ac:dyDescent="0.25">
-      <c r="A168" s="28">
-        <v>5174</v>
-      </c>
+      <c r="A168" s="28"/>
       <c r="B168" s="29" t="s">
         <v>901</v>
       </c>
@@ -20849,9 +20457,7 @@
       <c r="AC168" s="30"/>
     </row>
     <row r="169" spans="1:29" ht="225" x14ac:dyDescent="0.25">
-      <c r="A169" s="28">
-        <v>5176</v>
-      </c>
+      <c r="A169" s="28"/>
       <c r="B169" s="29" t="s">
         <v>902</v>
       </c>
@@ -20908,9 +20514,7 @@
       <c r="AC169" s="30"/>
     </row>
     <row r="170" spans="1:29" ht="135" x14ac:dyDescent="0.25">
-      <c r="A170" s="28">
-        <v>5177</v>
-      </c>
+      <c r="A170" s="28"/>
       <c r="B170" s="29" t="s">
         <v>903</v>
       </c>
@@ -20967,9 +20571,7 @@
       <c r="AC170" s="30"/>
     </row>
     <row r="171" spans="1:29" ht="225" x14ac:dyDescent="0.25">
-      <c r="A171" s="28">
-        <v>5179</v>
-      </c>
+      <c r="A171" s="28"/>
       <c r="B171" s="29" t="s">
         <v>904</v>
       </c>
@@ -21026,9 +20628,7 @@
       <c r="AC171" s="30"/>
     </row>
     <row r="172" spans="1:29" ht="135" x14ac:dyDescent="0.25">
-      <c r="A172" s="28">
-        <v>5180</v>
-      </c>
+      <c r="A172" s="28"/>
       <c r="B172" s="29" t="s">
         <v>905</v>
       </c>
@@ -21085,9 +20685,7 @@
       <c r="AC172" s="30"/>
     </row>
     <row r="173" spans="1:29" ht="225" x14ac:dyDescent="0.25">
-      <c r="A173" s="28">
-        <v>5182</v>
-      </c>
+      <c r="A173" s="28"/>
       <c r="B173" s="29" t="s">
         <v>906</v>
       </c>
@@ -21144,9 +20742,7 @@
       <c r="AC173" s="30"/>
     </row>
     <row r="174" spans="1:29" ht="150" x14ac:dyDescent="0.25">
-      <c r="A174" s="28">
-        <v>5183</v>
-      </c>
+      <c r="A174" s="28"/>
       <c r="B174" s="29" t="s">
         <v>907</v>
       </c>
@@ -21203,9 +20799,7 @@
       <c r="AC174" s="30"/>
     </row>
     <row r="175" spans="1:29" ht="150" x14ac:dyDescent="0.25">
-      <c r="A175" s="28">
-        <v>5184</v>
-      </c>
+      <c r="A175" s="28"/>
       <c r="B175" s="29" t="s">
         <v>908</v>
       </c>
@@ -21262,9 +20856,7 @@
       <c r="AC175" s="30"/>
     </row>
     <row r="176" spans="1:29" ht="150" x14ac:dyDescent="0.25">
-      <c r="A176" s="28">
-        <v>5185</v>
-      </c>
+      <c r="A176" s="28"/>
       <c r="B176" s="29" t="s">
         <v>909</v>
       </c>
@@ -21321,9 +20913,7 @@
       <c r="AC176" s="30"/>
     </row>
     <row r="177" spans="1:29" ht="150" x14ac:dyDescent="0.25">
-      <c r="A177" s="28">
-        <v>5186</v>
-      </c>
+      <c r="A177" s="28"/>
       <c r="B177" s="29" t="s">
         <v>910</v>
       </c>
@@ -21380,9 +20970,7 @@
       <c r="AC177" s="30"/>
     </row>
     <row r="178" spans="1:29" ht="75" x14ac:dyDescent="0.25">
-      <c r="A178" s="28">
-        <v>5187</v>
-      </c>
+      <c r="A178" s="28"/>
       <c r="B178" s="29" t="s">
         <v>911</v>
       </c>
@@ -21439,9 +21027,7 @@
       <c r="AC178" s="30"/>
     </row>
     <row r="179" spans="1:29" ht="75" x14ac:dyDescent="0.25">
-      <c r="A179" s="28">
-        <v>5188</v>
-      </c>
+      <c r="A179" s="28"/>
       <c r="B179" s="29" t="s">
         <v>912</v>
       </c>
@@ -21498,9 +21084,7 @@
       <c r="AC179" s="30"/>
     </row>
     <row r="180" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A180" s="28">
-        <v>5189</v>
-      </c>
+      <c r="A180" s="28"/>
       <c r="B180" s="29" t="s">
         <v>913</v>
       </c>
@@ -21557,9 +21141,7 @@
       <c r="AC180" s="30"/>
     </row>
     <row r="181" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A181" s="28">
-        <v>5190</v>
-      </c>
+      <c r="A181" s="28"/>
       <c r="B181" s="29" t="s">
         <v>914</v>
       </c>
@@ -21620,9 +21202,7 @@
       <c r="AC181" s="30"/>
     </row>
     <row r="182" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A182" s="28">
-        <v>5191</v>
-      </c>
+      <c r="A182" s="28"/>
       <c r="B182" s="29" t="s">
         <v>915</v>
       </c>
@@ -21681,9 +21261,7 @@
       <c r="AC182" s="30"/>
     </row>
     <row r="183" spans="1:29" ht="210" x14ac:dyDescent="0.25">
-      <c r="A183" s="28">
-        <v>5376</v>
-      </c>
+      <c r="A183" s="28"/>
       <c r="B183" s="29" t="s">
         <v>916</v>
       </c>
@@ -21740,9 +21318,7 @@
       <c r="AC183" s="30"/>
     </row>
     <row r="184" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A184" s="28">
-        <v>5380</v>
-      </c>
+      <c r="A184" s="28"/>
       <c r="B184" s="29" t="s">
         <v>917</v>
       </c>
@@ -21799,9 +21375,7 @@
       <c r="AC184" s="30"/>
     </row>
     <row r="185" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A185" s="28">
-        <v>5381</v>
-      </c>
+      <c r="A185" s="28"/>
       <c r="B185" s="29" t="s">
         <v>918</v>
       </c>
@@ -21858,9 +21432,7 @@
       <c r="AC185" s="30"/>
     </row>
     <row r="186" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A186" s="28">
-        <v>5383</v>
-      </c>
+      <c r="A186" s="28"/>
       <c r="B186" s="29" t="s">
         <v>919</v>
       </c>
@@ -21917,9 +21489,7 @@
       <c r="AC186" s="30"/>
     </row>
     <row r="187" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A187" s="28">
-        <v>5384</v>
-      </c>
+      <c r="A187" s="28"/>
       <c r="B187" s="29" t="s">
         <v>920</v>
       </c>
@@ -21976,9 +21546,7 @@
       <c r="AC187" s="30"/>
     </row>
     <row r="188" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A188" s="28">
-        <v>5385</v>
-      </c>
+      <c r="A188" s="28"/>
       <c r="B188" s="29" t="s">
         <v>921</v>
       </c>
@@ -22035,9 +21603,7 @@
       <c r="AC188" s="30"/>
     </row>
     <row r="189" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A189" s="28">
-        <v>5386</v>
-      </c>
+      <c r="A189" s="28"/>
       <c r="B189" s="29" t="s">
         <v>922</v>
       </c>
@@ -22094,9 +21660,7 @@
       <c r="AC189" s="30"/>
     </row>
     <row r="190" spans="1:29" ht="60" x14ac:dyDescent="0.25">
-      <c r="A190" s="28">
-        <v>5387</v>
-      </c>
+      <c r="A190" s="28"/>
       <c r="B190" s="29" t="s">
         <v>923</v>
       </c>
@@ -22153,9 +21717,7 @@
       <c r="AC190" s="30"/>
     </row>
     <row r="191" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A191" s="28">
-        <v>5388</v>
-      </c>
+      <c r="A191" s="28"/>
       <c r="B191" s="29" t="s">
         <v>924</v>
       </c>
@@ -22212,9 +21774,7 @@
       <c r="AC191" s="30"/>
     </row>
     <row r="192" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A192" s="28">
-        <v>5389</v>
-      </c>
+      <c r="A192" s="28"/>
       <c r="B192" s="29" t="s">
         <v>925</v>
       </c>
@@ -22271,9 +21831,7 @@
       <c r="AC192" s="30"/>
     </row>
     <row r="193" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A193" s="28">
-        <v>5390</v>
-      </c>
+      <c r="A193" s="28"/>
       <c r="B193" s="29" t="s">
         <v>926</v>
       </c>
@@ -22330,9 +21888,7 @@
       <c r="AC193" s="30"/>
     </row>
     <row r="194" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A194" s="28">
-        <v>5391</v>
-      </c>
+      <c r="A194" s="28"/>
       <c r="B194" s="29" t="s">
         <v>927</v>
       </c>
@@ -22387,9 +21943,7 @@
       <c r="AC194" s="30"/>
     </row>
     <row r="195" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A195" s="28">
-        <v>5392</v>
-      </c>
+      <c r="A195" s="28"/>
       <c r="B195" s="29" t="s">
         <v>928</v>
       </c>
@@ -22446,9 +22000,7 @@
       <c r="AC195" s="30"/>
     </row>
     <row r="196" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A196" s="28">
-        <v>5394</v>
-      </c>
+      <c r="A196" s="28"/>
       <c r="B196" s="29" t="s">
         <v>929</v>
       </c>
@@ -22505,9 +22057,7 @@
       <c r="AC196" s="30"/>
     </row>
     <row r="197" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A197" s="28">
-        <v>5397</v>
-      </c>
+      <c r="A197" s="28"/>
       <c r="B197" s="29" t="s">
         <v>930</v>
       </c>
@@ -22564,9 +22114,7 @@
       <c r="AC197" s="30"/>
     </row>
     <row r="198" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A198" s="28">
-        <v>5398</v>
-      </c>
+      <c r="A198" s="28"/>
       <c r="B198" s="29" t="s">
         <v>931</v>
       </c>
@@ -22623,9 +22171,7 @@
       <c r="AC198" s="30"/>
     </row>
     <row r="199" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A199" s="28">
-        <v>5399</v>
-      </c>
+      <c r="A199" s="28"/>
       <c r="B199" s="29" t="s">
         <v>932</v>
       </c>
@@ -22682,9 +22228,7 @@
       <c r="AC199" s="30"/>
     </row>
     <row r="200" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A200" s="28">
-        <v>5400</v>
-      </c>
+      <c r="A200" s="28"/>
       <c r="B200" s="29" t="s">
         <v>933</v>
       </c>
@@ -22741,9 +22285,7 @@
       <c r="AC200" s="30"/>
     </row>
     <row r="201" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A201" s="28">
-        <v>5401</v>
-      </c>
+      <c r="A201" s="28"/>
       <c r="B201" s="29" t="s">
         <v>934</v>
       </c>
@@ -22800,9 +22342,7 @@
       <c r="AC201" s="30"/>
     </row>
     <row r="202" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A202" s="28">
-        <v>5402</v>
-      </c>
+      <c r="A202" s="28"/>
       <c r="B202" s="29" t="s">
         <v>935</v>
       </c>
@@ -22859,9 +22399,7 @@
       <c r="AC202" s="30"/>
     </row>
     <row r="203" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A203" s="28">
-        <v>5403</v>
-      </c>
+      <c r="A203" s="28"/>
       <c r="B203" s="29" t="s">
         <v>936</v>
       </c>
@@ -22918,9 +22456,7 @@
       <c r="AC203" s="30"/>
     </row>
     <row r="204" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A204" s="28">
-        <v>5404</v>
-      </c>
+      <c r="A204" s="28"/>
       <c r="B204" s="29" t="s">
         <v>937</v>
       </c>
@@ -22977,9 +22513,7 @@
       <c r="AC204" s="30"/>
     </row>
     <row r="205" spans="1:29" ht="60" x14ac:dyDescent="0.25">
-      <c r="A205" s="28">
-        <v>5405</v>
-      </c>
+      <c r="A205" s="28"/>
       <c r="B205" s="29" t="s">
         <v>938</v>
       </c>
@@ -23036,9 +22570,7 @@
       <c r="AC205" s="30"/>
     </row>
     <row r="206" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A206" s="28">
-        <v>5406</v>
-      </c>
+      <c r="A206" s="28"/>
       <c r="B206" s="29" t="s">
         <v>939</v>
       </c>
@@ -23095,9 +22627,7 @@
       <c r="AC206" s="30"/>
     </row>
     <row r="207" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A207" s="28">
-        <v>5407</v>
-      </c>
+      <c r="A207" s="28"/>
       <c r="B207" s="29" t="s">
         <v>940</v>
       </c>
@@ -23154,9 +22684,7 @@
       <c r="AC207" s="30"/>
     </row>
     <row r="208" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A208" s="28">
-        <v>18432</v>
-      </c>
+      <c r="A208" s="28"/>
       <c r="B208" s="29" t="s">
         <v>1283</v>
       </c>
@@ -23205,9 +22733,7 @@
       <c r="AC208" s="30"/>
     </row>
     <row r="209" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A209" s="28">
-        <v>18433</v>
-      </c>
+      <c r="A209" s="28"/>
       <c r="B209" s="29" t="s">
         <v>1284</v>
       </c>
@@ -23256,9 +22782,7 @@
       <c r="AC209" s="30"/>
     </row>
     <row r="210" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A210" s="28">
-        <v>18434</v>
-      </c>
+      <c r="A210" s="28"/>
       <c r="B210" s="29" t="s">
         <v>1285</v>
       </c>
@@ -23307,9 +22831,7 @@
       <c r="AC210" s="30"/>
     </row>
     <row r="211" spans="1:29" ht="90" x14ac:dyDescent="0.25">
-      <c r="A211" s="28">
-        <v>18435</v>
-      </c>
+      <c r="A211" s="28"/>
       <c r="B211" s="29" t="s">
         <v>1286</v>
       </c>
@@ -23360,9 +22882,7 @@
       <c r="AC211" s="30"/>
     </row>
     <row r="212" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A212" s="28">
-        <v>18436</v>
-      </c>
+      <c r="A212" s="28"/>
       <c r="B212" s="29" t="s">
         <v>1287</v>
       </c>
@@ -23411,9 +22931,7 @@
       <c r="AC212" s="30"/>
     </row>
     <row r="213" spans="1:29" ht="90" x14ac:dyDescent="0.25">
-      <c r="A213" s="28">
-        <v>18437</v>
-      </c>
+      <c r="A213" s="28"/>
       <c r="B213" s="29" t="s">
         <v>1288</v>
       </c>
@@ -23464,9 +22982,7 @@
       <c r="AC213" s="30"/>
     </row>
     <row r="214" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A214" s="28">
-        <v>18438</v>
-      </c>
+      <c r="A214" s="28"/>
       <c r="B214" s="29" t="s">
         <v>1289</v>
       </c>
@@ -23515,9 +23031,7 @@
       <c r="AC214" s="30"/>
     </row>
     <row r="215" spans="1:29" ht="90" x14ac:dyDescent="0.25">
-      <c r="A215" s="28">
-        <v>18439</v>
-      </c>
+      <c r="A215" s="28"/>
       <c r="B215" s="29" t="s">
         <v>1290</v>
       </c>
@@ -23568,9 +23082,7 @@
       <c r="AC215" s="30"/>
     </row>
     <row r="216" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A216" s="28">
-        <v>18440</v>
-      </c>
+      <c r="A216" s="28"/>
       <c r="B216" s="29" t="s">
         <v>1291</v>
       </c>
@@ -23619,9 +23131,7 @@
       <c r="AC216" s="30"/>
     </row>
     <row r="217" spans="1:29" ht="90" x14ac:dyDescent="0.25">
-      <c r="A217" s="28">
-        <v>18441</v>
-      </c>
+      <c r="A217" s="28"/>
       <c r="B217" s="29" t="s">
         <v>1292</v>
       </c>
@@ -23672,9 +23182,7 @@
       <c r="AC217" s="30"/>
     </row>
     <row r="218" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A218" s="28">
-        <v>18442</v>
-      </c>
+      <c r="A218" s="28"/>
       <c r="B218" s="29" t="s">
         <v>1293</v>
       </c>
@@ -23725,9 +23233,7 @@
       <c r="AC218" s="30"/>
     </row>
     <row r="219" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A219" s="28">
-        <v>18443</v>
-      </c>
+      <c r="A219" s="28"/>
       <c r="B219" s="29" t="s">
         <v>1294</v>
       </c>
@@ -23778,9 +23284,7 @@
       <c r="AC219" s="30"/>
     </row>
     <row r="220" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A220" s="28">
-        <v>18444</v>
-      </c>
+      <c r="A220" s="28"/>
       <c r="B220" s="29" t="s">
         <v>1295</v>
       </c>
@@ -23831,9 +23335,7 @@
       <c r="AC220" s="30"/>
     </row>
     <row r="221" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A221" s="28">
-        <v>18445</v>
-      </c>
+      <c r="A221" s="28"/>
       <c r="B221" s="29" t="s">
         <v>1296</v>
       </c>
@@ -23884,9 +23386,7 @@
       <c r="AC221" s="30"/>
     </row>
     <row r="222" spans="1:29" ht="270" x14ac:dyDescent="0.25">
-      <c r="A222" s="28">
-        <v>18446</v>
-      </c>
+      <c r="A222" s="28"/>
       <c r="B222" s="29" t="s">
         <v>941</v>
       </c>
@@ -23939,9 +23439,7 @@
       <c r="AC222" s="30"/>
     </row>
     <row r="223" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A223" s="28">
-        <v>18447</v>
-      </c>
+      <c r="A223" s="28"/>
       <c r="B223" s="29" t="s">
         <v>942</v>
       </c>
@@ -23994,9 +23492,7 @@
       <c r="AC223" s="30"/>
     </row>
     <row r="224" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A224" s="28">
-        <v>18448</v>
-      </c>
+      <c r="A224" s="28"/>
       <c r="B224" s="29" t="s">
         <v>943</v>
       </c>
@@ -24049,9 +23545,7 @@
       <c r="AC224" s="30"/>
     </row>
     <row r="225" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A225" s="28">
-        <v>18449</v>
-      </c>
+      <c r="A225" s="28"/>
       <c r="B225" s="29" t="s">
         <v>1297</v>
       </c>
@@ -24102,9 +23596,7 @@
       <c r="AC225" s="30"/>
     </row>
     <row r="226" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A226" s="28">
-        <v>18450</v>
-      </c>
+      <c r="A226" s="28"/>
       <c r="B226" s="29" t="s">
         <v>1298</v>
       </c>
@@ -24155,9 +23647,7 @@
       <c r="AC226" s="30"/>
     </row>
     <row r="227" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A227" s="28">
-        <v>18451</v>
-      </c>
+      <c r="A227" s="28"/>
       <c r="B227" s="29" t="s">
         <v>1299</v>
       </c>
@@ -24208,9 +23698,7 @@
       <c r="AC227" s="30"/>
     </row>
     <row r="228" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A228" s="28">
-        <v>18452</v>
-      </c>
+      <c r="A228" s="28"/>
       <c r="B228" s="29" t="s">
         <v>1300</v>
       </c>
@@ -24261,9 +23749,7 @@
       <c r="AC228" s="30"/>
     </row>
     <row r="229" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A229" s="28">
-        <v>18453</v>
-      </c>
+      <c r="A229" s="28"/>
       <c r="B229" s="29" t="s">
         <v>1301</v>
       </c>
@@ -24314,9 +23800,7 @@
       <c r="AC229" s="30"/>
     </row>
     <row r="230" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A230" s="28">
-        <v>18454</v>
-      </c>
+      <c r="A230" s="28"/>
       <c r="B230" s="29" t="s">
         <v>1302</v>
       </c>
@@ -24367,9 +23851,7 @@
       <c r="AC230" s="30"/>
     </row>
     <row r="231" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A231" s="28">
-        <v>18455</v>
-      </c>
+      <c r="A231" s="28"/>
       <c r="B231" s="29" t="s">
         <v>1303</v>
       </c>
@@ -24420,9 +23902,7 @@
       <c r="AC231" s="30"/>
     </row>
     <row r="232" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A232" s="28">
-        <v>18456</v>
-      </c>
+      <c r="A232" s="28"/>
       <c r="B232" s="29" t="s">
         <v>1304</v>
       </c>
@@ -24473,9 +23953,7 @@
       <c r="AC232" s="30"/>
     </row>
     <row r="233" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A233" s="28">
-        <v>18457</v>
-      </c>
+      <c r="A233" s="28"/>
       <c r="B233" s="29" t="s">
         <v>1305</v>
       </c>
@@ -24526,9 +24004,7 @@
       <c r="AC233" s="30"/>
     </row>
     <row r="234" spans="1:29" ht="60" x14ac:dyDescent="0.25">
-      <c r="A234" s="28">
-        <v>19458</v>
-      </c>
+      <c r="A234" s="28"/>
       <c r="B234" s="37" t="s">
         <v>1149</v>
       </c>
@@ -24764,9 +24240,7 @@
       </c>
     </row>
     <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="28">
-        <v>512</v>
-      </c>
+      <c r="A2" s="28"/>
       <c r="B2" s="29" t="s">
         <v>945</v>
       </c>
@@ -24819,9 +24293,7 @@
       <c r="AC2" s="30"/>
     </row>
     <row r="3" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="28">
-        <v>513</v>
-      </c>
+      <c r="A3" s="28"/>
       <c r="B3" s="29" t="s">
         <v>946</v>
       </c>
@@ -24882,9 +24354,7 @@
       <c r="AC3" s="30"/>
     </row>
     <row r="4" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
-        <v>514</v>
-      </c>
+      <c r="A4" s="28"/>
       <c r="B4" s="29" t="s">
         <v>947</v>
       </c>
@@ -24943,9 +24413,7 @@
       <c r="AC4" s="30"/>
     </row>
     <row r="5" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="28">
-        <v>515</v>
-      </c>
+      <c r="A5" s="28"/>
       <c r="B5" s="29" t="s">
         <v>948</v>
       </c>
@@ -25006,9 +24474,7 @@
       <c r="AC5" s="30"/>
     </row>
     <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
-        <v>516</v>
-      </c>
+      <c r="A6" s="28"/>
       <c r="B6" s="29" t="s">
         <v>949</v>
       </c>
@@ -25069,9 +24535,7 @@
       <c r="AC6" s="30"/>
     </row>
     <row r="7" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
-        <v>517</v>
-      </c>
+      <c r="A7" s="28"/>
       <c r="B7" s="29" t="s">
         <v>950</v>
       </c>
@@ -25130,9 +24594,7 @@
       <c r="AC7" s="30"/>
     </row>
     <row r="8" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
-        <v>518</v>
-      </c>
+      <c r="A8" s="28"/>
       <c r="B8" s="29" t="s">
         <v>951</v>
       </c>
@@ -25191,9 +24653,7 @@
       <c r="AC8" s="30"/>
     </row>
     <row r="9" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
-        <v>519</v>
-      </c>
+      <c r="A9" s="28"/>
       <c r="B9" s="29" t="s">
         <v>952</v>
       </c>
@@ -25252,9 +24712,7 @@
       <c r="AC9" s="30"/>
     </row>
     <row r="10" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
-        <v>520</v>
-      </c>
+      <c r="A10" s="28"/>
       <c r="B10" s="29" t="s">
         <v>953</v>
       </c>
@@ -25313,9 +24771,7 @@
       <c r="AC10" s="30"/>
     </row>
     <row r="11" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="28">
-        <v>528</v>
-      </c>
+      <c r="A11" s="28"/>
       <c r="B11" s="29" t="s">
         <v>954</v>
       </c>
@@ -25368,9 +24824,7 @@
       <c r="AC11" s="30"/>
     </row>
     <row r="12" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="28">
-        <v>529</v>
-      </c>
+      <c r="A12" s="28"/>
       <c r="B12" s="29" t="s">
         <v>955</v>
       </c>
@@ -25423,9 +24877,7 @@
       <c r="AC12" s="30"/>
     </row>
     <row r="13" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="28">
-        <v>530</v>
-      </c>
+      <c r="A13" s="28"/>
       <c r="B13" s="29" t="s">
         <v>956</v>
       </c>
@@ -25478,9 +24930,7 @@
       <c r="AC13" s="30"/>
     </row>
     <row r="14" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
-        <v>531</v>
-      </c>
+      <c r="A14" s="28"/>
       <c r="B14" s="29" t="s">
         <v>957</v>
       </c>
@@ -25533,9 +24983,7 @@
       <c r="AC14" s="30"/>
     </row>
     <row r="15" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="28">
-        <v>768</v>
-      </c>
+      <c r="A15" s="28"/>
       <c r="B15" s="29" t="s">
         <v>958</v>
       </c>
@@ -25596,9 +25044,7 @@
       <c r="AC15" s="30"/>
     </row>
     <row r="16" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="28">
-        <v>769</v>
-      </c>
+      <c r="A16" s="28"/>
       <c r="B16" s="29" t="s">
         <v>959</v>
       </c>
@@ -25649,9 +25095,7 @@
       <c r="AC16" s="30"/>
     </row>
     <row r="17" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="28">
-        <v>770</v>
-      </c>
+      <c r="A17" s="28"/>
       <c r="B17" s="29" t="s">
         <v>960</v>
       </c>
@@ -25712,9 +25156,7 @@
       <c r="AC17" s="30"/>
     </row>
     <row r="18" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="28">
-        <v>771</v>
-      </c>
+      <c r="A18" s="28"/>
       <c r="B18" s="29" t="s">
         <v>961</v>
       </c>
@@ -25765,9 +25207,7 @@
       <c r="AC18" s="30"/>
     </row>
     <row r="19" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="28">
-        <v>772</v>
-      </c>
+      <c r="A19" s="28"/>
       <c r="B19" s="29" t="s">
         <v>962</v>
       </c>
@@ -25820,9 +25260,7 @@
       <c r="AC19" s="30"/>
     </row>
     <row r="20" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="28">
-        <v>1024</v>
-      </c>
+      <c r="A20" s="28"/>
       <c r="B20" s="29" t="s">
         <v>963</v>
       </c>
@@ -25881,9 +25319,7 @@
       <c r="AC20" s="30"/>
     </row>
     <row r="21" spans="1:29" ht="105" x14ac:dyDescent="0.25">
-      <c r="A21" s="28">
-        <v>1025</v>
-      </c>
+      <c r="A21" s="28"/>
       <c r="B21" s="29" t="s">
         <v>964</v>
       </c>
@@ -25934,9 +25370,7 @@
       <c r="AC21" s="30"/>
     </row>
     <row r="22" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="28">
-        <v>1026</v>
-      </c>
+      <c r="A22" s="28"/>
       <c r="B22" s="29" t="s">
         <v>965</v>
       </c>
@@ -25987,9 +25421,7 @@
       <c r="AC22" s="30"/>
     </row>
     <row r="23" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="28">
-        <v>1027</v>
-      </c>
+      <c r="A23" s="28"/>
       <c r="B23" s="29" t="s">
         <v>966</v>
       </c>
@@ -26040,9 +25472,7 @@
       <c r="AC23" s="30"/>
     </row>
     <row r="24" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="28">
-        <v>1028</v>
-      </c>
+      <c r="A24" s="28"/>
       <c r="B24" s="29" t="s">
         <v>967</v>
       </c>
@@ -26093,9 +25523,7 @@
       <c r="AC24" s="30"/>
     </row>
     <row r="25" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="28">
-        <v>1029</v>
-      </c>
+      <c r="A25" s="28"/>
       <c r="B25" s="29" t="s">
         <v>968</v>
       </c>
@@ -26146,9 +25574,7 @@
       <c r="AC25" s="30"/>
     </row>
     <row r="26" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="28">
-        <v>1030</v>
-      </c>
+      <c r="A26" s="28"/>
       <c r="B26" s="29" t="s">
         <v>969</v>
       </c>
@@ -26199,9 +25625,7 @@
       <c r="AC26" s="30"/>
     </row>
     <row r="27" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="28">
-        <v>1031</v>
-      </c>
+      <c r="A27" s="28"/>
       <c r="B27" s="29" t="s">
         <v>970</v>
       </c>
@@ -26252,9 +25676,7 @@
       <c r="AC27" s="30"/>
     </row>
     <row r="28" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="28">
-        <v>1032</v>
-      </c>
+      <c r="A28" s="28"/>
       <c r="B28" s="29" t="s">
         <v>971</v>
       </c>
@@ -26305,9 +25727,7 @@
       <c r="AC28" s="30"/>
     </row>
     <row r="29" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="28">
-        <v>1033</v>
-      </c>
+      <c r="A29" s="28"/>
       <c r="B29" s="29" t="s">
         <v>972</v>
       </c>
@@ -26358,9 +25778,7 @@
       <c r="AC29" s="30"/>
     </row>
     <row r="30" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="28">
-        <v>1034</v>
-      </c>
+      <c r="A30" s="28"/>
       <c r="B30" s="29" t="s">
         <v>973</v>
       </c>
@@ -26411,9 +25829,7 @@
       <c r="AC30" s="30"/>
     </row>
     <row r="31" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="28">
-        <v>1035</v>
-      </c>
+      <c r="A31" s="28"/>
       <c r="B31" s="29" t="s">
         <v>974</v>
       </c>
@@ -26464,9 +25880,7 @@
       <c r="AC31" s="30"/>
     </row>
     <row r="32" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="28">
-        <v>1036</v>
-      </c>
+      <c r="A32" s="28"/>
       <c r="B32" s="29" t="s">
         <v>975</v>
       </c>
@@ -26517,9 +25931,7 @@
       <c r="AC32" s="30"/>
     </row>
     <row r="33" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="28">
-        <v>1037</v>
-      </c>
+      <c r="A33" s="28"/>
       <c r="B33" s="29" t="s">
         <v>976</v>
       </c>
@@ -26570,9 +25982,7 @@
       <c r="AC33" s="30"/>
     </row>
     <row r="34" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="28">
-        <v>1038</v>
-      </c>
+      <c r="A34" s="28"/>
       <c r="B34" s="29" t="s">
         <v>977</v>
       </c>
@@ -26623,9 +26033,7 @@
       <c r="AC34" s="30"/>
     </row>
     <row r="35" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="28">
-        <v>1039</v>
-      </c>
+      <c r="A35" s="28"/>
       <c r="B35" s="29" t="s">
         <v>978</v>
       </c>
@@ -26676,9 +26084,7 @@
       <c r="AC35" s="30"/>
     </row>
     <row r="36" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="28">
-        <v>1040</v>
-      </c>
+      <c r="A36" s="28"/>
       <c r="B36" s="29" t="s">
         <v>979</v>
       </c>
@@ -26729,9 +26135,7 @@
       <c r="AC36" s="30"/>
     </row>
     <row r="37" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="28">
-        <v>1041</v>
-      </c>
+      <c r="A37" s="28"/>
       <c r="B37" s="29" t="s">
         <v>980</v>
       </c>
@@ -26782,9 +26186,7 @@
       <c r="AC37" s="30"/>
     </row>
     <row r="38" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="28">
-        <v>1042</v>
-      </c>
+      <c r="A38" s="28"/>
       <c r="B38" s="29" t="s">
         <v>981</v>
       </c>
@@ -26835,9 +26237,7 @@
       <c r="AC38" s="30"/>
     </row>
     <row r="39" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="28">
-        <v>1043</v>
-      </c>
+      <c r="A39" s="28"/>
       <c r="B39" s="29" t="s">
         <v>982</v>
       </c>
@@ -26888,9 +26288,7 @@
       <c r="AC39" s="30"/>
     </row>
     <row r="40" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="28">
-        <v>1044</v>
-      </c>
+      <c r="A40" s="28"/>
       <c r="B40" s="29" t="s">
         <v>983</v>
       </c>
@@ -26941,9 +26339,7 @@
       <c r="AC40" s="30"/>
     </row>
     <row r="41" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="28">
-        <v>1045</v>
-      </c>
+      <c r="A41" s="28"/>
       <c r="B41" s="29" t="s">
         <v>984</v>
       </c>
@@ -26994,9 +26390,7 @@
       <c r="AC41" s="30"/>
     </row>
     <row r="42" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="28">
-        <v>1046</v>
-      </c>
+      <c r="A42" s="28"/>
       <c r="B42" s="29" t="s">
         <v>985</v>
       </c>
@@ -27047,9 +26441,7 @@
       <c r="AC42" s="30"/>
     </row>
     <row r="43" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="28">
-        <v>1047</v>
-      </c>
+      <c r="A43" s="28"/>
       <c r="B43" s="29" t="s">
         <v>986</v>
       </c>
@@ -27100,9 +26492,7 @@
       <c r="AC43" s="30"/>
     </row>
     <row r="44" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="28">
-        <v>1048</v>
-      </c>
+      <c r="A44" s="28"/>
       <c r="B44" s="29" t="s">
         <v>987</v>
       </c>
@@ -27153,9 +26543,7 @@
       <c r="AC44" s="30"/>
     </row>
     <row r="45" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="28">
-        <v>1049</v>
-      </c>
+      <c r="A45" s="28"/>
       <c r="B45" s="29" t="s">
         <v>988</v>
       </c>
@@ -27240,9 +26628,7 @@
       </c>
     </row>
     <row r="46" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="28">
-        <v>1050</v>
-      </c>
+      <c r="A46" s="28"/>
       <c r="B46" s="29" t="s">
         <v>989</v>
       </c>
@@ -27293,9 +26679,7 @@
       <c r="AC46" s="30"/>
     </row>
     <row r="47" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="28">
-        <v>1051</v>
-      </c>
+      <c r="A47" s="28"/>
       <c r="B47" s="29" t="s">
         <v>990</v>
       </c>
@@ -27346,9 +26730,7 @@
       <c r="AC47" s="30"/>
     </row>
     <row r="48" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="28">
-        <v>1052</v>
-      </c>
+      <c r="A48" s="28"/>
       <c r="B48" s="29" t="s">
         <v>991</v>
       </c>
@@ -27399,9 +26781,7 @@
       <c r="AC48" s="30"/>
     </row>
     <row r="49" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="28">
-        <v>1053</v>
-      </c>
+      <c r="A49" s="28"/>
       <c r="B49" s="29" t="s">
         <v>992</v>
       </c>
@@ -27452,9 +26832,7 @@
       <c r="AC49" s="30"/>
     </row>
     <row r="50" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="28">
-        <v>1054</v>
-      </c>
+      <c r="A50" s="28"/>
       <c r="B50" s="29" t="s">
         <v>993</v>
       </c>
@@ -27505,9 +26883,7 @@
       <c r="AC50" s="30"/>
     </row>
     <row r="51" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="28">
-        <v>1055</v>
-      </c>
+      <c r="A51" s="28"/>
       <c r="B51" s="29" t="s">
         <v>994</v>
       </c>
@@ -27558,9 +26934,7 @@
       <c r="AC51" s="30"/>
     </row>
     <row r="52" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="28">
-        <v>1056</v>
-      </c>
+      <c r="A52" s="28"/>
       <c r="B52" s="29" t="s">
         <v>995</v>
       </c>
@@ -27611,9 +26985,7 @@
       <c r="AC52" s="30"/>
     </row>
     <row r="53" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="28">
-        <v>1057</v>
-      </c>
+      <c r="A53" s="28"/>
       <c r="B53" s="29" t="s">
         <v>996</v>
       </c>
@@ -27664,9 +27036,7 @@
       <c r="AC53" s="30"/>
     </row>
     <row r="54" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="28">
-        <v>1058</v>
-      </c>
+      <c r="A54" s="28"/>
       <c r="B54" s="29" t="s">
         <v>997</v>
       </c>
@@ -27717,9 +27087,7 @@
       <c r="AC54" s="30"/>
     </row>
     <row r="55" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="28">
-        <v>1059</v>
-      </c>
+      <c r="A55" s="28"/>
       <c r="B55" s="29" t="s">
         <v>998</v>
       </c>
@@ -27770,9 +27138,7 @@
       <c r="AC55" s="30"/>
     </row>
     <row r="56" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="28">
-        <v>1060</v>
-      </c>
+      <c r="A56" s="28"/>
       <c r="B56" s="29" t="s">
         <v>999</v>
       </c>
@@ -27823,9 +27189,7 @@
       <c r="AC56" s="30"/>
     </row>
     <row r="57" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="28">
-        <v>1061</v>
-      </c>
+      <c r="A57" s="28"/>
       <c r="B57" s="29" t="s">
         <v>1000</v>
       </c>
@@ -27876,9 +27240,7 @@
       <c r="AC57" s="30"/>
     </row>
     <row r="58" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="28">
-        <v>1062</v>
-      </c>
+      <c r="A58" s="28"/>
       <c r="B58" s="29" t="s">
         <v>1001</v>
       </c>
@@ -27929,9 +27291,7 @@
       <c r="AC58" s="30"/>
     </row>
     <row r="59" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="28">
-        <v>1063</v>
-      </c>
+      <c r="A59" s="28"/>
       <c r="B59" s="29" t="s">
         <v>1002</v>
       </c>
@@ -27982,9 +27342,7 @@
       <c r="AC59" s="30"/>
     </row>
     <row r="60" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="28">
-        <v>1064</v>
-      </c>
+      <c r="A60" s="28"/>
       <c r="B60" s="29" t="s">
         <v>1003</v>
       </c>
@@ -28035,9 +27393,7 @@
       <c r="AC60" s="30"/>
     </row>
     <row r="61" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="28">
-        <v>1065</v>
-      </c>
+      <c r="A61" s="28"/>
       <c r="B61" s="29" t="s">
         <v>1004</v>
       </c>
@@ -28088,9 +27444,7 @@
       <c r="AC61" s="30"/>
     </row>
     <row r="62" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="28">
-        <v>1066</v>
-      </c>
+      <c r="A62" s="28"/>
       <c r="B62" s="29" t="s">
         <v>1005</v>
       </c>
@@ -28141,9 +27495,7 @@
       <c r="AC62" s="30"/>
     </row>
     <row r="63" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="28">
-        <v>1067</v>
-      </c>
+      <c r="A63" s="28"/>
       <c r="B63" s="29" t="s">
         <v>1006</v>
       </c>
@@ -28194,9 +27546,7 @@
       <c r="AC63" s="30"/>
     </row>
     <row r="64" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64" s="28">
-        <v>1068</v>
-      </c>
+      <c r="A64" s="28"/>
       <c r="B64" s="29" t="s">
         <v>1007</v>
       </c>
@@ -28247,9 +27597,7 @@
       <c r="AC64" s="30"/>
     </row>
     <row r="65" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="28">
-        <v>1069</v>
-      </c>
+      <c r="A65" s="28"/>
       <c r="B65" s="29" t="s">
         <v>1008</v>
       </c>
@@ -28300,9 +27648,7 @@
       <c r="AC65" s="30"/>
     </row>
     <row r="66" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A66" s="28">
-        <v>1070</v>
-      </c>
+      <c r="A66" s="28"/>
       <c r="B66" s="29" t="s">
         <v>1009</v>
       </c>
@@ -28353,9 +27699,7 @@
       <c r="AC66" s="30"/>
     </row>
     <row r="67" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="28">
-        <v>1071</v>
-      </c>
+      <c r="A67" s="28"/>
       <c r="B67" s="29" t="s">
         <v>1010</v>
       </c>
@@ -28406,9 +27750,7 @@
       <c r="AC67" s="30"/>
     </row>
     <row r="68" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="28">
-        <v>1072</v>
-      </c>
+      <c r="A68" s="28"/>
       <c r="B68" s="29" t="s">
         <v>1011</v>
       </c>
@@ -28459,9 +27801,7 @@
       <c r="AC68" s="30"/>
     </row>
     <row r="69" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="28">
-        <v>1073</v>
-      </c>
+      <c r="A69" s="28"/>
       <c r="B69" s="29" t="s">
         <v>1012</v>
       </c>
@@ -28512,9 +27852,7 @@
       <c r="AC69" s="30"/>
     </row>
     <row r="70" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="28">
-        <v>1099</v>
-      </c>
+      <c r="A70" s="28"/>
       <c r="B70" s="29" t="s">
         <v>1013</v>
       </c>
@@ -28573,9 +27911,7 @@
       <c r="AC70" s="30"/>
     </row>
     <row r="71" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A71" s="28">
-        <v>1100</v>
-      </c>
+      <c r="A71" s="28"/>
       <c r="B71" s="29" t="s">
         <v>1014</v>
       </c>
@@ -28634,9 +27970,7 @@
       <c r="AC71" s="30"/>
     </row>
     <row r="72" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A72" s="28">
-        <v>1101</v>
-      </c>
+      <c r="A72" s="28"/>
       <c r="B72" s="29" t="s">
         <v>1015</v>
       </c>
@@ -28695,9 +28029,7 @@
       <c r="AC72" s="30"/>
     </row>
     <row r="73" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A73" s="28">
-        <v>1102</v>
-      </c>
+      <c r="A73" s="28"/>
       <c r="B73" s="29" t="s">
         <v>1016</v>
       </c>
@@ -28756,9 +28088,7 @@
       <c r="AC73" s="30"/>
     </row>
     <row r="74" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A74" s="28">
-        <v>1103</v>
-      </c>
+      <c r="A74" s="28"/>
       <c r="B74" s="29" t="s">
         <v>1017</v>
       </c>
@@ -28817,9 +28147,7 @@
       <c r="AC74" s="30"/>
     </row>
     <row r="75" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A75" s="28">
-        <v>1104</v>
-      </c>
+      <c r="A75" s="28"/>
       <c r="B75" s="29" t="s">
         <v>1018</v>
       </c>
@@ -28878,9 +28206,7 @@
       <c r="AC75" s="30"/>
     </row>
     <row r="76" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A76" s="28">
-        <v>1105</v>
-      </c>
+      <c r="A76" s="28"/>
       <c r="B76" s="29" t="s">
         <v>1019</v>
       </c>
@@ -28939,9 +28265,7 @@
       <c r="AC76" s="30"/>
     </row>
     <row r="77" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A77" s="28">
-        <v>1106</v>
-      </c>
+      <c r="A77" s="28"/>
       <c r="B77" s="29" t="s">
         <v>1020</v>
       </c>
@@ -29000,9 +28324,7 @@
       <c r="AC77" s="30"/>
     </row>
     <row r="78" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A78" s="28">
-        <v>1107</v>
-      </c>
+      <c r="A78" s="28"/>
       <c r="B78" s="29" t="s">
         <v>1021</v>
       </c>
@@ -29061,9 +28383,7 @@
       <c r="AC78" s="30"/>
     </row>
     <row r="79" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A79" s="28">
-        <v>1108</v>
-      </c>
+      <c r="A79" s="28"/>
       <c r="B79" s="29" t="s">
         <v>1022</v>
       </c>
@@ -29122,9 +28442,7 @@
       <c r="AC79" s="30"/>
     </row>
     <row r="80" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A80" s="28">
-        <v>1109</v>
-      </c>
+      <c r="A80" s="28"/>
       <c r="B80" s="29" t="s">
         <v>1023</v>
       </c>
@@ -29183,9 +28501,7 @@
       <c r="AC80" s="30"/>
     </row>
     <row r="81" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A81" s="28">
-        <v>1110</v>
-      </c>
+      <c r="A81" s="28"/>
       <c r="B81" s="29" t="s">
         <v>1024</v>
       </c>
@@ -29244,9 +28560,7 @@
       <c r="AC81" s="30"/>
     </row>
     <row r="82" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A82" s="28">
-        <v>1111</v>
-      </c>
+      <c r="A82" s="28"/>
       <c r="B82" s="29" t="s">
         <v>1025</v>
       </c>
@@ -29305,9 +28619,7 @@
       <c r="AC82" s="30"/>
     </row>
     <row r="83" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A83" s="28">
-        <v>1112</v>
-      </c>
+      <c r="A83" s="28"/>
       <c r="B83" s="29" t="s">
         <v>1026</v>
       </c>
@@ -29366,9 +28678,7 @@
       <c r="AC83" s="30"/>
     </row>
     <row r="84" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A84" s="28">
-        <v>1113</v>
-      </c>
+      <c r="A84" s="28"/>
       <c r="B84" s="29" t="s">
         <v>1027</v>
       </c>
@@ -29427,9 +28737,7 @@
       <c r="AC84" s="30"/>
     </row>
     <row r="85" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A85" s="28">
-        <v>1114</v>
-      </c>
+      <c r="A85" s="28"/>
       <c r="B85" s="29" t="s">
         <v>1028</v>
       </c>
@@ -29488,9 +28796,7 @@
       <c r="AC85" s="30"/>
     </row>
     <row r="86" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A86" s="28">
-        <v>1115</v>
-      </c>
+      <c r="A86" s="28"/>
       <c r="B86" s="29" t="s">
         <v>1029</v>
       </c>
@@ -29549,9 +28855,7 @@
       <c r="AC86" s="30"/>
     </row>
     <row r="87" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A87" s="28">
-        <v>1116</v>
-      </c>
+      <c r="A87" s="28"/>
       <c r="B87" s="29" t="s">
         <v>1030</v>
       </c>
@@ -29610,9 +28914,7 @@
       <c r="AC87" s="30"/>
     </row>
     <row r="88" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A88" s="28">
-        <v>1117</v>
-      </c>
+      <c r="A88" s="28"/>
       <c r="B88" s="29" t="s">
         <v>1031</v>
       </c>
@@ -29671,9 +28973,7 @@
       <c r="AC88" s="30"/>
     </row>
     <row r="89" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A89" s="28">
-        <v>1118</v>
-      </c>
+      <c r="A89" s="28"/>
       <c r="B89" s="29" t="s">
         <v>1032</v>
       </c>
@@ -29732,9 +29032,7 @@
       <c r="AC89" s="30"/>
     </row>
     <row r="90" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A90" s="28">
-        <v>1119</v>
-      </c>
+      <c r="A90" s="28"/>
       <c r="B90" s="29" t="s">
         <v>1033</v>
       </c>
@@ -29793,9 +29091,7 @@
       <c r="AC90" s="30"/>
     </row>
     <row r="91" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A91" s="28">
-        <v>1120</v>
-      </c>
+      <c r="A91" s="28"/>
       <c r="B91" s="29" t="s">
         <v>1034</v>
       </c>
@@ -29854,9 +29150,7 @@
       <c r="AC91" s="30"/>
     </row>
     <row r="92" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A92" s="28">
-        <v>1121</v>
-      </c>
+      <c r="A92" s="28"/>
       <c r="B92" s="29" t="s">
         <v>1035</v>
       </c>
@@ -29915,9 +29209,7 @@
       <c r="AC92" s="30"/>
     </row>
     <row r="93" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A93" s="28">
-        <v>1122</v>
-      </c>
+      <c r="A93" s="28"/>
       <c r="B93" s="29" t="s">
         <v>1036</v>
       </c>
@@ -29976,9 +29268,7 @@
       <c r="AC93" s="30"/>
     </row>
     <row r="94" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A94" s="28">
-        <v>1123</v>
-      </c>
+      <c r="A94" s="28"/>
       <c r="B94" s="29" t="s">
         <v>1037</v>
       </c>
@@ -30037,9 +29327,7 @@
       <c r="AC94" s="30"/>
     </row>
     <row r="95" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A95" s="28">
-        <v>1200</v>
-      </c>
+      <c r="A95" s="28"/>
       <c r="B95" s="29" t="s">
         <v>1038</v>
       </c>
@@ -30090,9 +29378,7 @@
       <c r="AC95" s="30"/>
     </row>
     <row r="96" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A96" s="28">
-        <v>1201</v>
-      </c>
+      <c r="A96" s="28"/>
       <c r="B96" s="29" t="s">
         <v>1039</v>
       </c>
@@ -30143,9 +29429,7 @@
       <c r="AC96" s="30"/>
     </row>
     <row r="97" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A97" s="28">
-        <v>1202</v>
-      </c>
+      <c r="A97" s="28"/>
       <c r="B97" s="29" t="s">
         <v>1040</v>
       </c>
@@ -30196,9 +29480,7 @@
       <c r="AC97" s="30"/>
     </row>
     <row r="98" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A98" s="28">
-        <v>1203</v>
-      </c>
+      <c r="A98" s="28"/>
       <c r="B98" s="29" t="s">
         <v>1041</v>
       </c>
@@ -30249,9 +29531,7 @@
       <c r="AC98" s="30"/>
     </row>
     <row r="99" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A99" s="28">
-        <v>1204</v>
-      </c>
+      <c r="A99" s="28"/>
       <c r="B99" s="29" t="s">
         <v>1042</v>
       </c>
@@ -30302,9 +29582,7 @@
       <c r="AC99" s="30"/>
     </row>
     <row r="100" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A100" s="28">
-        <v>1205</v>
-      </c>
+      <c r="A100" s="28"/>
       <c r="B100" s="29" t="s">
         <v>1043</v>
       </c>
@@ -30355,9 +29633,7 @@
       <c r="AC100" s="30"/>
     </row>
     <row r="101" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A101" s="28">
-        <v>1206</v>
-      </c>
+      <c r="A101" s="28"/>
       <c r="B101" s="29" t="s">
         <v>1044</v>
       </c>
@@ -30408,9 +29684,7 @@
       <c r="AC101" s="30"/>
     </row>
     <row r="102" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A102" s="28">
-        <v>1207</v>
-      </c>
+      <c r="A102" s="28"/>
       <c r="B102" s="29" t="s">
         <v>1045</v>
       </c>
@@ -30461,9 +29735,7 @@
       <c r="AC102" s="30"/>
     </row>
     <row r="103" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A103" s="28">
-        <v>1208</v>
-      </c>
+      <c r="A103" s="28"/>
       <c r="B103" s="29" t="s">
         <v>1046</v>
       </c>
@@ -30514,9 +29786,7 @@
       <c r="AC103" s="30"/>
     </row>
     <row r="104" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A104" s="28">
-        <v>1209</v>
-      </c>
+      <c r="A104" s="28"/>
       <c r="B104" s="29" t="s">
         <v>1047</v>
       </c>
@@ -30567,9 +29837,7 @@
       <c r="AC104" s="30"/>
     </row>
     <row r="105" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A105" s="28">
-        <v>1210</v>
-      </c>
+      <c r="A105" s="28"/>
       <c r="B105" s="29" t="s">
         <v>1048</v>
       </c>
@@ -30620,9 +29888,7 @@
       <c r="AC105" s="30"/>
     </row>
     <row r="106" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A106" s="28">
-        <v>1211</v>
-      </c>
+      <c r="A106" s="28"/>
       <c r="B106" s="29" t="s">
         <v>1049</v>
       </c>
@@ -30673,9 +29939,7 @@
       <c r="AC106" s="30"/>
     </row>
     <row r="107" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A107" s="28">
-        <v>1212</v>
-      </c>
+      <c r="A107" s="28"/>
       <c r="B107" s="29" t="s">
         <v>1050</v>
       </c>
@@ -30726,9 +29990,7 @@
       <c r="AC107" s="30"/>
     </row>
     <row r="108" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A108" s="28">
-        <v>1213</v>
-      </c>
+      <c r="A108" s="28"/>
       <c r="B108" s="29" t="s">
         <v>1051</v>
       </c>
@@ -30779,9 +30041,7 @@
       <c r="AC108" s="30"/>
     </row>
     <row r="109" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A109" s="28">
-        <v>1214</v>
-      </c>
+      <c r="A109" s="28"/>
       <c r="B109" s="29" t="s">
         <v>1052</v>
       </c>
@@ -30832,9 +30092,7 @@
       <c r="AC109" s="30"/>
     </row>
     <row r="110" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A110" s="28">
-        <v>1215</v>
-      </c>
+      <c r="A110" s="28"/>
       <c r="B110" s="29" t="s">
         <v>1053</v>
       </c>
@@ -30885,9 +30143,7 @@
       <c r="AC110" s="30"/>
     </row>
     <row r="111" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A111" s="28">
-        <v>1216</v>
-      </c>
+      <c r="A111" s="28"/>
       <c r="B111" s="29" t="s">
         <v>1054</v>
       </c>
@@ -30938,9 +30194,7 @@
       <c r="AC111" s="30"/>
     </row>
     <row r="112" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A112" s="28">
-        <v>1217</v>
-      </c>
+      <c r="A112" s="28"/>
       <c r="B112" s="29" t="s">
         <v>1055</v>
       </c>
@@ -30991,9 +30245,7 @@
       <c r="AC112" s="30"/>
     </row>
     <row r="113" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A113" s="28">
-        <v>1218</v>
-      </c>
+      <c r="A113" s="28"/>
       <c r="B113" s="29" t="s">
         <v>1056</v>
       </c>
@@ -31044,9 +30296,7 @@
       <c r="AC113" s="30"/>
     </row>
     <row r="114" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A114" s="28">
-        <v>1219</v>
-      </c>
+      <c r="A114" s="28"/>
       <c r="B114" s="29" t="s">
         <v>1057</v>
       </c>
@@ -31097,9 +30347,7 @@
       <c r="AC114" s="30"/>
     </row>
     <row r="115" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A115" s="28">
-        <v>1220</v>
-      </c>
+      <c r="A115" s="28"/>
       <c r="B115" s="29" t="s">
         <v>1058</v>
       </c>
@@ -31150,9 +30398,7 @@
       <c r="AC115" s="30"/>
     </row>
     <row r="116" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A116" s="28">
-        <v>1221</v>
-      </c>
+      <c r="A116" s="28"/>
       <c r="B116" s="29" t="s">
         <v>1059</v>
       </c>
@@ -31203,9 +30449,7 @@
       <c r="AC116" s="30"/>
     </row>
     <row r="117" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A117" s="28">
-        <v>1222</v>
-      </c>
+      <c r="A117" s="28"/>
       <c r="B117" s="29" t="s">
         <v>1060</v>
       </c>
@@ -31256,9 +30500,7 @@
       <c r="AC117" s="30"/>
     </row>
     <row r="118" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A118" s="28">
-        <v>1223</v>
-      </c>
+      <c r="A118" s="28"/>
       <c r="B118" s="29" t="s">
         <v>1061</v>
       </c>
@@ -31309,9 +30551,7 @@
       <c r="AC118" s="30"/>
     </row>
     <row r="119" spans="1:29" ht="60" x14ac:dyDescent="0.25">
-      <c r="A119" s="28">
-        <v>1584</v>
-      </c>
+      <c r="A119" s="28"/>
       <c r="B119" s="29" t="s">
         <v>1062</v>
       </c>
@@ -31366,9 +30606,7 @@
       <c r="AC119" s="30"/>
     </row>
     <row r="120" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A120" s="28">
-        <v>1585</v>
-      </c>
+      <c r="A120" s="28"/>
       <c r="B120" s="29" t="s">
         <v>1063</v>
       </c>
@@ -31429,9 +30667,7 @@
       <c r="AC120" s="30"/>
     </row>
     <row r="121" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A121" s="28">
-        <v>1586</v>
-      </c>
+      <c r="A121" s="28"/>
       <c r="B121" s="29" t="s">
         <v>1064</v>
       </c>
@@ -31492,9 +30728,7 @@
       <c r="AC121" s="30"/>
     </row>
     <row r="122" spans="1:29" ht="105" x14ac:dyDescent="0.25">
-      <c r="A122" s="28">
-        <v>16384</v>
-      </c>
+      <c r="A122" s="28"/>
       <c r="B122" s="29" t="s">
         <v>1065</v>
       </c>
@@ -31545,9 +30779,7 @@
       <c r="AC122" s="30"/>
     </row>
     <row r="123" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A123" s="28">
-        <v>16385</v>
-      </c>
+      <c r="A123" s="28"/>
       <c r="B123" s="29" t="s">
         <v>1066</v>
       </c>
@@ -31598,9 +30830,7 @@
       <c r="AC123" s="30"/>
     </row>
     <row r="124" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A124" s="28">
-        <v>16386</v>
-      </c>
+      <c r="A124" s="28"/>
       <c r="B124" s="29" t="s">
         <v>1067</v>
       </c>
@@ -31651,9 +30881,7 @@
       <c r="AC124" s="30"/>
     </row>
     <row r="125" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A125" s="28">
-        <v>16387</v>
-      </c>
+      <c r="A125" s="28"/>
       <c r="B125" s="29" t="s">
         <v>1068</v>
       </c>
@@ -31704,9 +30932,7 @@
       <c r="AC125" s="30"/>
     </row>
     <row r="126" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A126" s="28">
-        <v>16388</v>
-      </c>
+      <c r="A126" s="28"/>
       <c r="B126" s="29" t="s">
         <v>1069</v>
       </c>
@@ -31757,9 +30983,7 @@
       <c r="AC126" s="30"/>
     </row>
     <row r="127" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A127" s="28">
-        <v>16389</v>
-      </c>
+      <c r="A127" s="28"/>
       <c r="B127" s="29" t="s">
         <v>1070</v>
       </c>
@@ -31810,9 +31034,7 @@
       <c r="AC127" s="30"/>
     </row>
     <row r="128" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="28">
-        <v>16390</v>
-      </c>
+      <c r="A128" s="28"/>
       <c r="B128" s="29" t="s">
         <v>1071</v>
       </c>
@@ -31863,9 +31085,7 @@
       <c r="AC128" s="30"/>
     </row>
     <row r="129" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A129" s="28">
-        <v>16391</v>
-      </c>
+      <c r="A129" s="28"/>
       <c r="B129" s="29" t="s">
         <v>1072</v>
       </c>
@@ -31916,9 +31136,7 @@
       <c r="AC129" s="30"/>
     </row>
     <row r="130" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A130" s="28">
-        <v>16392</v>
-      </c>
+      <c r="A130" s="28"/>
       <c r="B130" s="29" t="s">
         <v>1073</v>
       </c>
@@ -31969,9 +31187,7 @@
       <c r="AC130" s="30"/>
     </row>
     <row r="131" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A131" s="28">
-        <v>16393</v>
-      </c>
+      <c r="A131" s="28"/>
       <c r="B131" s="29" t="s">
         <v>1074</v>
       </c>
@@ -32022,9 +31238,7 @@
       <c r="AC131" s="30"/>
     </row>
     <row r="132" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A132" s="28">
-        <v>16394</v>
-      </c>
+      <c r="A132" s="28"/>
       <c r="B132" s="29" t="s">
         <v>1075</v>
       </c>
@@ -32075,9 +31289,7 @@
       <c r="AC132" s="30"/>
     </row>
     <row r="133" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A133" s="28">
-        <v>16395</v>
-      </c>
+      <c r="A133" s="28"/>
       <c r="B133" s="29" t="s">
         <v>1076</v>
       </c>
@@ -32128,9 +31340,7 @@
       <c r="AC133" s="30"/>
     </row>
     <row r="134" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A134" s="28">
-        <v>16396</v>
-      </c>
+      <c r="A134" s="28"/>
       <c r="B134" s="29" t="s">
         <v>1077</v>
       </c>
@@ -32181,9 +31391,7 @@
       <c r="AC134" s="30"/>
     </row>
     <row r="135" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A135" s="28">
-        <v>16397</v>
-      </c>
+      <c r="A135" s="28"/>
       <c r="B135" s="29" t="s">
         <v>1078</v>
       </c>
@@ -32234,9 +31442,7 @@
       <c r="AC135" s="30"/>
     </row>
     <row r="136" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A136" s="28">
-        <v>16398</v>
-      </c>
+      <c r="A136" s="28"/>
       <c r="B136" s="29" t="s">
         <v>1079</v>
       </c>
@@ -32287,9 +31493,7 @@
       <c r="AC136" s="30"/>
     </row>
     <row r="137" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A137" s="28">
-        <v>16399</v>
-      </c>
+      <c r="A137" s="28"/>
       <c r="B137" s="29" t="s">
         <v>1080</v>
       </c>
@@ -32340,9 +31544,7 @@
       <c r="AC137" s="30"/>
     </row>
     <row r="138" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A138" s="28">
-        <v>16400</v>
-      </c>
+      <c r="A138" s="28"/>
       <c r="B138" s="29" t="s">
         <v>1081</v>
       </c>
@@ -32393,9 +31595,7 @@
       <c r="AC138" s="30"/>
     </row>
     <row r="139" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A139" s="28">
-        <v>16401</v>
-      </c>
+      <c r="A139" s="28"/>
       <c r="B139" s="29" t="s">
         <v>1082</v>
       </c>
@@ -32446,9 +31646,7 @@
       <c r="AC139" s="30"/>
     </row>
     <row r="140" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A140" s="28">
-        <v>16402</v>
-      </c>
+      <c r="A140" s="28"/>
       <c r="B140" s="29" t="s">
         <v>1083</v>
       </c>
@@ -32499,9 +31697,7 @@
       <c r="AC140" s="30"/>
     </row>
     <row r="141" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A141" s="28">
-        <v>16403</v>
-      </c>
+      <c r="A141" s="28"/>
       <c r="B141" s="29" t="s">
         <v>1084</v>
       </c>
@@ -32552,9 +31748,7 @@
       <c r="AC141" s="30"/>
     </row>
     <row r="142" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A142" s="28">
-        <v>16404</v>
-      </c>
+      <c r="A142" s="28"/>
       <c r="B142" s="29" t="s">
         <v>1085</v>
       </c>
@@ -32605,9 +31799,7 @@
       <c r="AC142" s="30"/>
     </row>
     <row r="143" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A143" s="28">
-        <v>16405</v>
-      </c>
+      <c r="A143" s="28"/>
       <c r="B143" s="29" t="s">
         <v>1086</v>
       </c>
@@ -32658,9 +31850,7 @@
       <c r="AC143" s="30"/>
     </row>
     <row r="144" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A144" s="28">
-        <v>16406</v>
-      </c>
+      <c r="A144" s="28"/>
       <c r="B144" s="29" t="s">
         <v>1087</v>
       </c>
@@ -32711,9 +31901,7 @@
       <c r="AC144" s="30"/>
     </row>
     <row r="145" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A145" s="28">
-        <v>16407</v>
-      </c>
+      <c r="A145" s="28"/>
       <c r="B145" s="29" t="s">
         <v>1088</v>
       </c>
@@ -32764,9 +31952,7 @@
       <c r="AC145" s="30"/>
     </row>
     <row r="146" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A146" s="28">
-        <v>16484</v>
-      </c>
+      <c r="A146" s="28"/>
       <c r="B146" s="29" t="s">
         <v>1089</v>
       </c>
@@ -32817,9 +32003,7 @@
       <c r="AC146" s="30"/>
     </row>
     <row r="147" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A147" s="28">
-        <v>16485</v>
-      </c>
+      <c r="A147" s="28"/>
       <c r="B147" s="29" t="s">
         <v>1090</v>
       </c>
@@ -32870,9 +32054,7 @@
       <c r="AC147" s="30"/>
     </row>
     <row r="148" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A148" s="28">
-        <v>16486</v>
-      </c>
+      <c r="A148" s="28"/>
       <c r="B148" s="29" t="s">
         <v>1091</v>
       </c>
@@ -32923,9 +32105,7 @@
       <c r="AC148" s="30"/>
     </row>
     <row r="149" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A149" s="28">
-        <v>16487</v>
-      </c>
+      <c r="A149" s="28"/>
       <c r="B149" s="29" t="s">
         <v>1092</v>
       </c>
@@ -32976,9 +32156,7 @@
       <c r="AC149" s="30"/>
     </row>
     <row r="150" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A150" s="28">
-        <v>16488</v>
-      </c>
+      <c r="A150" s="28"/>
       <c r="B150" s="29" t="s">
         <v>1093</v>
       </c>
@@ -33029,9 +32207,7 @@
       <c r="AC150" s="30"/>
     </row>
     <row r="151" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A151" s="28">
-        <v>16489</v>
-      </c>
+      <c r="A151" s="28"/>
       <c r="B151" s="29" t="s">
         <v>1094</v>
       </c>
@@ -33082,9 +32258,7 @@
       <c r="AC151" s="30"/>
     </row>
     <row r="152" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A152" s="28">
-        <v>16490</v>
-      </c>
+      <c r="A152" s="28"/>
       <c r="B152" s="29" t="s">
         <v>1095</v>
       </c>
@@ -33135,9 +32309,7 @@
       <c r="AC152" s="30"/>
     </row>
     <row r="153" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A153" s="28">
-        <v>16491</v>
-      </c>
+      <c r="A153" s="28"/>
       <c r="B153" s="29" t="s">
         <v>1096</v>
       </c>
@@ -33188,9 +32360,7 @@
       <c r="AC153" s="30"/>
     </row>
     <row r="154" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A154" s="28">
-        <v>16492</v>
-      </c>
+      <c r="A154" s="28"/>
       <c r="B154" s="29" t="s">
         <v>1097</v>
       </c>
@@ -33241,9 +32411,7 @@
       <c r="AC154" s="30"/>
     </row>
     <row r="155" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A155" s="28">
-        <v>16493</v>
-      </c>
+      <c r="A155" s="28"/>
       <c r="B155" s="29" t="s">
         <v>1098</v>
       </c>
@@ -33294,9 +32462,7 @@
       <c r="AC155" s="30"/>
     </row>
     <row r="156" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A156" s="28">
-        <v>16494</v>
-      </c>
+      <c r="A156" s="28"/>
       <c r="B156" s="29" t="s">
         <v>1099</v>
       </c>
@@ -33347,9 +32513,7 @@
       <c r="AC156" s="30"/>
     </row>
     <row r="157" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A157" s="28">
-        <v>16495</v>
-      </c>
+      <c r="A157" s="28"/>
       <c r="B157" s="29" t="s">
         <v>1100</v>
       </c>
@@ -33400,9 +32564,7 @@
       <c r="AC157" s="30"/>
     </row>
     <row r="158" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A158" s="28">
-        <v>16496</v>
-      </c>
+      <c r="A158" s="28"/>
       <c r="B158" s="29" t="s">
         <v>1101</v>
       </c>
@@ -33453,9 +32615,7 @@
       <c r="AC158" s="30"/>
     </row>
     <row r="159" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A159" s="28">
-        <v>16497</v>
-      </c>
+      <c r="A159" s="28"/>
       <c r="B159" s="29" t="s">
         <v>1102</v>
       </c>
@@ -33506,9 +32666,7 @@
       <c r="AC159" s="30"/>
     </row>
     <row r="160" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A160" s="28">
-        <v>16498</v>
-      </c>
+      <c r="A160" s="28"/>
       <c r="B160" s="29" t="s">
         <v>1103</v>
       </c>
@@ -33559,9 +32717,7 @@
       <c r="AC160" s="30"/>
     </row>
     <row r="161" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A161" s="28">
-        <v>16499</v>
-      </c>
+      <c r="A161" s="28"/>
       <c r="B161" s="29" t="s">
         <v>1104</v>
       </c>
@@ -33612,9 +32768,7 @@
       <c r="AC161" s="30"/>
     </row>
     <row r="162" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A162" s="28">
-        <v>16500</v>
-      </c>
+      <c r="A162" s="28"/>
       <c r="B162" s="29" t="s">
         <v>1105</v>
       </c>
@@ -33665,9 +32819,7 @@
       <c r="AC162" s="30"/>
     </row>
     <row r="163" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A163" s="28">
-        <v>16501</v>
-      </c>
+      <c r="A163" s="28"/>
       <c r="B163" s="29" t="s">
         <v>1106</v>
       </c>
@@ -33718,9 +32870,7 @@
       <c r="AC163" s="30"/>
     </row>
     <row r="164" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A164" s="28">
-        <v>16502</v>
-      </c>
+      <c r="A164" s="28"/>
       <c r="B164" s="29" t="s">
         <v>1107</v>
       </c>
@@ -33771,9 +32921,7 @@
       <c r="AC164" s="30"/>
     </row>
     <row r="165" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A165" s="28">
-        <v>16503</v>
-      </c>
+      <c r="A165" s="28"/>
       <c r="B165" s="29" t="s">
         <v>1108</v>
       </c>
@@ -33824,9 +32972,7 @@
       <c r="AC165" s="30"/>
     </row>
     <row r="166" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A166" s="28">
-        <v>16504</v>
-      </c>
+      <c r="A166" s="28"/>
       <c r="B166" s="29" t="s">
         <v>1109</v>
       </c>
@@ -33877,9 +33023,7 @@
       <c r="AC166" s="30"/>
     </row>
     <row r="167" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A167" s="28">
-        <v>16505</v>
-      </c>
+      <c r="A167" s="28"/>
       <c r="B167" s="29" t="s">
         <v>1110</v>
       </c>
@@ -33930,9 +33074,7 @@
       <c r="AC167" s="30"/>
     </row>
     <row r="168" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A168" s="28">
-        <v>16506</v>
-      </c>
+      <c r="A168" s="28"/>
       <c r="B168" s="29" t="s">
         <v>1111</v>
       </c>
@@ -33983,9 +33125,7 @@
       <c r="AC168" s="30"/>
     </row>
     <row r="169" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A169" s="28">
-        <v>16507</v>
-      </c>
+      <c r="A169" s="28"/>
       <c r="B169" s="29" t="s">
         <v>1112</v>
       </c>
@@ -34036,9 +33176,7 @@
       <c r="AC169" s="30"/>
     </row>
     <row r="170" spans="1:29" ht="60" x14ac:dyDescent="0.25">
-      <c r="A170" s="28">
-        <v>16784</v>
-      </c>
+      <c r="A170" s="28"/>
       <c r="B170" s="29" t="s">
         <v>1113</v>
       </c>
@@ -34097,9 +33235,7 @@
       <c r="AC170" s="30"/>
     </row>
     <row r="171" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A171" s="28">
-        <v>16785</v>
-      </c>
+      <c r="A171" s="28"/>
       <c r="B171" s="29" t="s">
         <v>1114</v>
       </c>
@@ -34150,9 +33286,7 @@
       <c r="AC171" s="30"/>
     </row>
     <row r="172" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A172" s="28">
-        <v>16786</v>
-      </c>
+      <c r="A172" s="28"/>
       <c r="B172" s="29" t="s">
         <v>1115</v>
       </c>
@@ -34203,9 +33337,7 @@
       <c r="AC172" s="30"/>
     </row>
     <row r="173" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A173" s="28">
-        <v>16787</v>
-      </c>
+      <c r="A173" s="28"/>
       <c r="B173" s="29" t="s">
         <v>1116</v>
       </c>
@@ -34256,9 +33388,7 @@
       <c r="AC173" s="30"/>
     </row>
     <row r="174" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A174" s="28">
-        <v>16788</v>
-      </c>
+      <c r="A174" s="28"/>
       <c r="B174" s="29" t="s">
         <v>1117</v>
       </c>
@@ -34309,9 +33439,7 @@
       <c r="AC174" s="30"/>
     </row>
     <row r="175" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A175" s="28">
-        <v>16789</v>
-      </c>
+      <c r="A175" s="28"/>
       <c r="B175" s="29" t="s">
         <v>1118</v>
       </c>
@@ -34362,9 +33490,7 @@
       <c r="AC175" s="30"/>
     </row>
     <row r="176" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A176" s="28">
-        <v>16790</v>
-      </c>
+      <c r="A176" s="28"/>
       <c r="B176" s="29" t="s">
         <v>1119</v>
       </c>
@@ -34415,9 +33541,7 @@
       <c r="AC176" s="30"/>
     </row>
     <row r="177" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A177" s="28">
-        <v>16791</v>
-      </c>
+      <c r="A177" s="28"/>
       <c r="B177" s="29" t="s">
         <v>1120</v>
       </c>
@@ -34468,9 +33592,7 @@
       <c r="AC177" s="30"/>
     </row>
     <row r="178" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A178" s="28">
-        <v>16792</v>
-      </c>
+      <c r="A178" s="28"/>
       <c r="B178" s="29" t="s">
         <v>1121</v>
       </c>
@@ -34521,9 +33643,7 @@
       <c r="AC178" s="30"/>
     </row>
     <row r="179" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A179" s="28">
-        <v>16793</v>
-      </c>
+      <c r="A179" s="28"/>
       <c r="B179" s="29" t="s">
         <v>1122</v>
       </c>
@@ -34574,9 +33694,7 @@
       <c r="AC179" s="30"/>
     </row>
     <row r="180" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A180" s="28">
-        <v>16794</v>
-      </c>
+      <c r="A180" s="28"/>
       <c r="B180" s="29" t="s">
         <v>1123</v>
       </c>
@@ -34627,9 +33745,7 @@
       <c r="AC180" s="30"/>
     </row>
     <row r="181" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A181" s="28">
-        <v>16795</v>
-      </c>
+      <c r="A181" s="28"/>
       <c r="B181" s="29" t="s">
         <v>1124</v>
       </c>
@@ -34680,9 +33796,7 @@
       <c r="AC181" s="30"/>
     </row>
     <row r="182" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A182" s="28">
-        <v>16796</v>
-      </c>
+      <c r="A182" s="28"/>
       <c r="B182" s="29" t="s">
         <v>1125</v>
       </c>
@@ -34733,9 +33847,7 @@
       <c r="AC182" s="30"/>
     </row>
     <row r="183" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A183" s="28">
-        <v>16797</v>
-      </c>
+      <c r="A183" s="28"/>
       <c r="B183" s="29" t="s">
         <v>1126</v>
       </c>
@@ -34786,9 +33898,7 @@
       <c r="AC183" s="30"/>
     </row>
     <row r="184" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A184" s="28">
-        <v>16798</v>
-      </c>
+      <c r="A184" s="28"/>
       <c r="B184" s="29" t="s">
         <v>1127</v>
       </c>
@@ -34839,9 +33949,7 @@
       <c r="AC184" s="30"/>
     </row>
     <row r="185" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A185" s="28">
-        <v>16799</v>
-      </c>
+      <c r="A185" s="28"/>
       <c r="B185" s="29" t="s">
         <v>1128</v>
       </c>
@@ -34892,9 +34000,7 @@
       <c r="AC185" s="30"/>
     </row>
     <row r="186" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A186" s="28">
-        <v>16800</v>
-      </c>
+      <c r="A186" s="28"/>
       <c r="B186" s="29" t="s">
         <v>1129</v>
       </c>
@@ -34945,9 +34051,7 @@
       <c r="AC186" s="30"/>
     </row>
     <row r="187" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A187" s="28">
-        <v>16801</v>
-      </c>
+      <c r="A187" s="28"/>
       <c r="B187" s="29" t="s">
         <v>1130</v>
       </c>
@@ -34998,9 +34102,7 @@
       <c r="AC187" s="30"/>
     </row>
     <row r="188" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A188" s="28">
-        <v>16802</v>
-      </c>
+      <c r="A188" s="28"/>
       <c r="B188" s="29" t="s">
         <v>1131</v>
       </c>
@@ -35051,9 +34153,7 @@
       <c r="AC188" s="30"/>
     </row>
     <row r="189" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A189" s="28">
-        <v>16803</v>
-      </c>
+      <c r="A189" s="28"/>
       <c r="B189" s="29" t="s">
         <v>1132</v>
       </c>
@@ -35104,9 +34204,7 @@
       <c r="AC189" s="30"/>
     </row>
     <row r="190" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A190" s="28">
-        <v>16804</v>
-      </c>
+      <c r="A190" s="28"/>
       <c r="B190" s="29" t="s">
         <v>1133</v>
       </c>
@@ -35157,9 +34255,7 @@
       <c r="AC190" s="30"/>
     </row>
     <row r="191" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A191" s="28">
-        <v>16805</v>
-      </c>
+      <c r="A191" s="28"/>
       <c r="B191" s="29" t="s">
         <v>1134</v>
       </c>
@@ -35210,9 +34306,7 @@
       <c r="AC191" s="30"/>
     </row>
     <row r="192" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A192" s="28">
-        <v>16806</v>
-      </c>
+      <c r="A192" s="28"/>
       <c r="B192" s="29" t="s">
         <v>1135</v>
       </c>
@@ -35263,9 +34357,7 @@
       <c r="AC192" s="30"/>
     </row>
     <row r="193" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A193" s="28">
-        <v>16807</v>
-      </c>
+      <c r="A193" s="28"/>
       <c r="B193" s="29" t="s">
         <v>1136</v>
       </c>
@@ -35316,9 +34408,7 @@
       <c r="AC193" s="30"/>
     </row>
     <row r="194" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A194" s="28">
-        <v>16808</v>
-      </c>
+      <c r="A194" s="28"/>
       <c r="B194" s="29" t="s">
         <v>1137</v>
       </c>
@@ -35369,9 +34459,7 @@
       <c r="AC194" s="30"/>
     </row>
     <row r="195" spans="1:29" ht="120" x14ac:dyDescent="0.25">
-      <c r="A195" s="28">
-        <v>4096</v>
-      </c>
+      <c r="A195" s="28"/>
       <c r="B195" s="29" t="s">
         <v>1138</v>
       </c>
@@ -35424,9 +34512,7 @@
       <c r="AC195" s="30"/>
     </row>
     <row r="196" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A196" s="28">
-        <v>4097</v>
-      </c>
+      <c r="A196" s="28"/>
       <c r="B196" s="29" t="s">
         <v>1139</v>
       </c>
@@ -35477,9 +34563,7 @@
       <c r="AC196" s="30"/>
     </row>
     <row r="197" spans="1:29" ht="105" x14ac:dyDescent="0.25">
-      <c r="A197" s="28">
-        <v>4098</v>
-      </c>
+      <c r="A197" s="28"/>
       <c r="B197" s="29" t="s">
         <v>1140</v>
       </c>
@@ -35532,9 +34616,7 @@
       <c r="AC197" s="30"/>
     </row>
     <row r="198" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A198" s="28">
-        <v>18944</v>
-      </c>
+      <c r="A198" s="28"/>
       <c r="B198" s="32" t="s">
         <v>1170</v>
       </c>
@@ -35587,9 +34669,7 @@
       <c r="AC198" s="28"/>
     </row>
     <row r="199" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A199" s="28">
-        <v>18946</v>
-      </c>
+      <c r="A199" s="28"/>
       <c r="B199" s="32" t="s">
         <v>1171</v>
       </c>
@@ -35642,9 +34722,7 @@
       <c r="AC199" s="28"/>
     </row>
     <row r="200" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A200" s="28">
-        <v>18947</v>
-      </c>
+      <c r="A200" s="28"/>
       <c r="B200" s="33" t="s">
         <v>1149</v>
       </c>
@@ -35699,9 +34777,7 @@
       <c r="AC200" s="28"/>
     </row>
     <row r="201" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A201" s="28">
-        <v>18948</v>
-      </c>
+      <c r="A201" s="28"/>
       <c r="B201" s="33" t="s">
         <v>1149</v>
       </c>
@@ -35756,9 +34832,7 @@
       <c r="AC201" s="28"/>
     </row>
     <row r="202" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A202" s="28">
-        <v>18949</v>
-      </c>
+      <c r="A202" s="28"/>
       <c r="B202" s="33" t="s">
         <v>1149</v>
       </c>
@@ -35811,9 +34885,7 @@
       <c r="AC202" s="28"/>
     </row>
     <row r="203" spans="1:29" ht="90" x14ac:dyDescent="0.25">
-      <c r="A203" s="28">
-        <v>18950</v>
-      </c>
+      <c r="A203" s="28"/>
       <c r="B203" s="33" t="s">
         <v>1149</v>
       </c>
@@ -35870,9 +34942,7 @@
       <c r="AC203" s="28"/>
     </row>
     <row r="204" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A204" s="28">
-        <v>18951</v>
-      </c>
+      <c r="A204" s="28"/>
       <c r="B204" s="33" t="s">
         <v>1149</v>
       </c>
@@ -35925,9 +34995,7 @@
       <c r="AC204" s="28"/>
     </row>
     <row r="205" spans="1:29" ht="90" x14ac:dyDescent="0.25">
-      <c r="A205" s="28">
-        <v>18952</v>
-      </c>
+      <c r="A205" s="28"/>
       <c r="B205" s="33" t="s">
         <v>1149</v>
       </c>
@@ -35984,9 +35052,7 @@
       <c r="AC205" s="28"/>
     </row>
     <row r="206" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A206" s="28">
-        <v>18953</v>
-      </c>
+      <c r="A206" s="28"/>
       <c r="B206" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36039,9 +35105,7 @@
       <c r="AC206" s="28"/>
     </row>
     <row r="207" spans="1:29" ht="90" x14ac:dyDescent="0.25">
-      <c r="A207" s="28">
-        <v>18954</v>
-      </c>
+      <c r="A207" s="28"/>
       <c r="B207" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36098,9 +35162,7 @@
       <c r="AC207" s="28"/>
     </row>
     <row r="208" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A208" s="28">
-        <v>18955</v>
-      </c>
+      <c r="A208" s="28"/>
       <c r="B208" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36153,9 +35215,7 @@
       <c r="AC208" s="28"/>
     </row>
     <row r="209" spans="1:29" ht="90" x14ac:dyDescent="0.25">
-      <c r="A209" s="28">
-        <v>18956</v>
-      </c>
+      <c r="A209" s="28"/>
       <c r="B209" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36212,9 +35272,7 @@
       <c r="AC209" s="28"/>
     </row>
     <row r="210" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A210" s="28">
-        <v>18957</v>
-      </c>
+      <c r="A210" s="28"/>
       <c r="B210" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36267,9 +35325,7 @@
       <c r="AC210" s="28"/>
     </row>
     <row r="211" spans="1:29" ht="90" x14ac:dyDescent="0.25">
-      <c r="A211" s="28">
-        <v>18958</v>
-      </c>
+      <c r="A211" s="28"/>
       <c r="B211" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36326,9 +35382,7 @@
       <c r="AC211" s="28"/>
     </row>
     <row r="212" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A212" s="28">
-        <v>18959</v>
-      </c>
+      <c r="A212" s="28"/>
       <c r="B212" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36381,9 +35435,7 @@
       <c r="AC212" s="28"/>
     </row>
     <row r="213" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A213" s="28">
-        <v>18960</v>
-      </c>
+      <c r="A213" s="28"/>
       <c r="B213" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36436,9 +35488,7 @@
       <c r="AC213" s="28"/>
     </row>
     <row r="214" spans="1:29" ht="75" x14ac:dyDescent="0.25">
-      <c r="A214" s="28">
-        <v>18961</v>
-      </c>
+      <c r="A214" s="28"/>
       <c r="B214" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36491,9 +35541,7 @@
       <c r="AC214" s="28"/>
     </row>
     <row r="215" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A215" s="28">
-        <v>18963</v>
-      </c>
+      <c r="A215" s="28"/>
       <c r="B215" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36550,9 +35598,7 @@
       <c r="AC215" s="28"/>
     </row>
     <row r="216" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A216" s="28">
-        <v>18964</v>
-      </c>
+      <c r="A216" s="28"/>
       <c r="B216" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36611,9 +35657,7 @@
       <c r="AC216" s="28"/>
     </row>
     <row r="217" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A217" s="28">
-        <v>18965</v>
-      </c>
+      <c r="A217" s="28"/>
       <c r="B217" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36672,9 +35716,7 @@
       <c r="AC217" s="28"/>
     </row>
     <row r="218" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A218" s="28">
-        <v>18966</v>
-      </c>
+      <c r="A218" s="28"/>
       <c r="B218" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36731,9 +35773,7 @@
       <c r="AC218" s="28"/>
     </row>
     <row r="219" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A219" s="28">
-        <v>19456</v>
-      </c>
+      <c r="A219" s="28"/>
       <c r="B219" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36792,9 +35832,7 @@
       <c r="AC219" s="28"/>
     </row>
     <row r="220" spans="1:29" ht="75" x14ac:dyDescent="0.25">
-      <c r="A220" s="28">
-        <v>19457</v>
-      </c>
+      <c r="A220" s="28"/>
       <c r="B220" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36853,9 +35891,7 @@
       <c r="AC220" s="28"/>
     </row>
     <row r="221" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A221" s="28">
-        <v>19712</v>
-      </c>
+      <c r="A221" s="28"/>
       <c r="B221" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36906,9 +35942,7 @@
       <c r="AC221" s="28"/>
     </row>
     <row r="222" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A222" s="28">
-        <v>19713</v>
-      </c>
+      <c r="A222" s="28"/>
       <c r="B222" s="33" t="s">
         <v>1149</v>
       </c>
@@ -36959,9 +35993,7 @@
       <c r="AC222" s="28"/>
     </row>
     <row r="223" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A223" s="28">
-        <v>19714</v>
-      </c>
+      <c r="A223" s="28"/>
       <c r="B223" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37016,9 +36048,7 @@
       <c r="AC223" s="28"/>
     </row>
     <row r="224" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A224" s="28">
-        <v>19719</v>
-      </c>
+      <c r="A224" s="28"/>
       <c r="B224" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37067,9 +36097,7 @@
       <c r="AC224" s="28"/>
     </row>
     <row r="225" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A225" s="28">
-        <v>19720</v>
-      </c>
+      <c r="A225" s="28"/>
       <c r="B225" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37118,9 +36146,7 @@
       <c r="AC225" s="28"/>
     </row>
     <row r="226" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A226" s="28">
-        <v>19723</v>
-      </c>
+      <c r="A226" s="28"/>
       <c r="B226" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37175,9 +36201,7 @@
       <c r="AC226" s="28"/>
     </row>
     <row r="227" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A227" s="28">
-        <v>19724</v>
-      </c>
+      <c r="A227" s="28"/>
       <c r="B227" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37232,9 +36256,7 @@
       <c r="AC227" s="28"/>
     </row>
     <row r="228" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A228" s="28">
-        <v>19725</v>
-      </c>
+      <c r="A228" s="28"/>
       <c r="B228" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37289,9 +36311,7 @@
       <c r="AC228" s="28"/>
     </row>
     <row r="229" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A229" s="28">
-        <v>19726</v>
-      </c>
+      <c r="A229" s="28"/>
       <c r="B229" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37346,9 +36366,7 @@
       <c r="AC229" s="28"/>
     </row>
     <row r="230" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A230" s="28">
-        <v>19727</v>
-      </c>
+      <c r="A230" s="28"/>
       <c r="B230" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37403,9 +36421,7 @@
       <c r="AC230" s="28"/>
     </row>
     <row r="231" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A231" s="28">
-        <v>19728</v>
-      </c>
+      <c r="A231" s="28"/>
       <c r="B231" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37460,9 +36476,7 @@
       <c r="AC231" s="28"/>
     </row>
     <row r="232" spans="1:29" ht="60" x14ac:dyDescent="0.25">
-      <c r="A232" s="28">
-        <v>19734</v>
-      </c>
+      <c r="A232" s="28"/>
       <c r="B232" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37517,9 +36531,7 @@
       <c r="AC232" s="28"/>
     </row>
     <row r="233" spans="1:29" ht="60" x14ac:dyDescent="0.25">
-      <c r="A233" s="28">
-        <v>19737</v>
-      </c>
+      <c r="A233" s="28"/>
       <c r="B233" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37574,9 +36586,7 @@
       <c r="AC233" s="28"/>
     </row>
     <row r="234" spans="1:29" ht="195" x14ac:dyDescent="0.25">
-      <c r="A234" s="28">
-        <v>19738</v>
-      </c>
+      <c r="A234" s="28"/>
       <c r="B234" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37631,9 +36641,7 @@
       <c r="AC234" s="28"/>
     </row>
     <row r="235" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A235" s="28">
-        <v>19740</v>
-      </c>
+      <c r="A235" s="28"/>
       <c r="B235" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37686,9 +36694,7 @@
       <c r="AC235" s="28"/>
     </row>
     <row r="236" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A236" s="28">
-        <v>19741</v>
-      </c>
+      <c r="A236" s="28"/>
       <c r="B236" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37743,9 +36749,7 @@
       <c r="AC236" s="28"/>
     </row>
     <row r="237" spans="1:29" ht="60" x14ac:dyDescent="0.25">
-      <c r="A237" s="28">
-        <v>19742</v>
-      </c>
+      <c r="A237" s="28"/>
       <c r="B237" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37798,9 +36802,7 @@
       <c r="AC237" s="28"/>
     </row>
     <row r="238" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A238" s="28">
-        <v>19743</v>
-      </c>
+      <c r="A238" s="28"/>
       <c r="B238" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37851,9 +36853,7 @@
       <c r="AC238" s="28"/>
     </row>
     <row r="239" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A239" s="28">
-        <v>19744</v>
-      </c>
+      <c r="A239" s="28"/>
       <c r="B239" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37904,9 +36904,7 @@
       <c r="AC239" s="28"/>
     </row>
     <row r="240" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A240" s="28">
-        <v>19745</v>
-      </c>
+      <c r="A240" s="28"/>
       <c r="B240" s="33" t="s">
         <v>1149</v>
       </c>
@@ -37961,9 +36959,7 @@
       <c r="AC240" s="28"/>
     </row>
     <row r="241" spans="1:29" ht="30" x14ac:dyDescent="0.25">
-      <c r="A241" s="28">
-        <v>19746</v>
-      </c>
+      <c r="A241" s="28"/>
       <c r="B241" s="33" t="s">
         <v>1149</v>
       </c>
@@ -38014,9 +37010,7 @@
       <c r="AC241" s="28"/>
     </row>
     <row r="242" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="20">
-        <v>19968</v>
-      </c>
+      <c r="A242" s="20"/>
       <c r="B242" s="23" t="s">
         <v>1149</v>
       </c>
@@ -38073,9 +37067,7 @@
       <c r="AC242" s="20"/>
     </row>
     <row r="243" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="20">
-        <v>19969</v>
-      </c>
+      <c r="A243" s="20"/>
       <c r="B243" s="23" t="s">
         <v>1149</v>
       </c>
@@ -38126,9 +37118,7 @@
       <c r="AC243" s="20"/>
     </row>
     <row r="244" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="20">
-        <v>19970</v>
-      </c>
+      <c r="A244" s="20"/>
       <c r="B244" s="23" t="s">
         <v>1149</v>
       </c>
@@ -38179,9 +37169,7 @@
       <c r="AC244" s="20"/>
     </row>
     <row r="245" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="20">
-        <v>19971</v>
-      </c>
+      <c r="A245" s="20"/>
       <c r="B245" s="23" t="s">
         <v>1149</v>
       </c>
@@ -38236,9 +37224,7 @@
       <c r="AC245" s="20"/>
     </row>
     <row r="246" spans="1:29" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A246" s="20">
-        <v>19972</v>
-      </c>
+      <c r="A246" s="20"/>
       <c r="B246" s="23" t="s">
         <v>1149</v>
       </c>
@@ -38291,9 +37277,7 @@
       <c r="AC246" s="20"/>
     </row>
     <row r="247" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="20">
-        <v>19973</v>
-      </c>
+      <c r="A247" s="20"/>
       <c r="B247" s="23" t="s">
         <v>1149</v>
       </c>
@@ -38344,9 +37328,7 @@
       <c r="AC247" s="20"/>
     </row>
     <row r="248" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="20">
-        <v>19974</v>
-      </c>
+      <c r="A248" s="20"/>
       <c r="B248" s="23" t="s">
         <v>1149</v>
       </c>
@@ -38397,9 +37379,7 @@
       <c r="AC248" s="20"/>
     </row>
     <row r="249" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="20">
-        <v>19975</v>
-      </c>
+      <c r="A249" s="20"/>
       <c r="B249" s="23" t="s">
         <v>1149</v>
       </c>
@@ -38456,9 +37436,7 @@
       <c r="AC249" s="20"/>
     </row>
     <row r="250" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A250" s="20">
-        <v>19976</v>
-      </c>
+      <c r="A250" s="20"/>
       <c r="B250" s="23" t="s">
         <v>1149</v>
       </c>
@@ -38513,9 +37491,7 @@
       <c r="AC250" s="20"/>
     </row>
     <row r="251" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="20">
-        <v>19977</v>
-      </c>
+      <c r="A251" s="20"/>
       <c r="B251" s="23" t="s">
         <v>1149</v>
       </c>
@@ -38572,9 +37548,7 @@
       <c r="AC251" s="20"/>
     </row>
     <row r="252" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A252" s="20">
-        <v>19978</v>
-      </c>
+      <c r="A252" s="20"/>
       <c r="B252" s="23" t="s">
         <v>1149</v>
       </c>
@@ -38627,9 +37601,7 @@
       <c r="AC252" s="20"/>
     </row>
     <row r="253" spans="1:29" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A253" s="20">
-        <v>19979</v>
-      </c>
+      <c r="A253" s="20"/>
       <c r="B253" s="23" t="s">
         <v>1149</v>
       </c>
@@ -38682,9 +37654,7 @@
       <c r="AC253" s="20"/>
     </row>
     <row r="254" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="20">
-        <v>19980</v>
-      </c>
+      <c r="A254" s="20"/>
       <c r="B254" s="23" t="s">
         <v>1149</v>
       </c>
@@ -38735,9 +37705,7 @@
       <c r="AC254" s="20"/>
     </row>
     <row r="255" spans="1:29" s="15" customFormat="1" ht="210" x14ac:dyDescent="0.25">
-      <c r="A255" s="20">
-        <v>19981</v>
-      </c>
+      <c r="A255" s="20"/>
       <c r="B255" s="23" t="s">
         <v>1149</v>
       </c>
